--- a/engineering/drainage-design/retention_volume/Retention_1200_File5_CrestSensitivity.xlsx
+++ b/engineering/drainage-design/retention_volume/Retention_1200_File5_CrestSensitivity.xlsx
@@ -2702,11 +2702,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F15,Compose_C3!$G$13:$G$64,1))+(F15-INDEX(Compose_C3!$G$13:$G$64,MATCH(F15,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F15,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F15,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F15,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F15,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F15,Compose_C3!$G$15:$G$66,1))+(F15-INDEX(Compose_C3!$G$15:$G$66,MATCH(F15,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F15,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F15,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F15,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F15,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C16,Compose_C3!$A$13:$A$64,1))+(C16-INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C16,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C16,Compose_C3!$A$15:$A$66,1))+(C16-INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C16,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -2718,11 +2718,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C16,Compose_C3!$A$13:$A$64,1))+(C16-INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C16,Compose_C3!$A$15:$A$66,1))+(C16-INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C16,Compose_C3!$A$13:$A$64,1))+(C16-INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C16,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C16,Compose_C3!$A$15:$A$66,1))+(C16-INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C16,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="15">
@@ -2740,11 +2740,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F16,Compose_C3!$G$13:$G$64,1))+(F16-INDEX(Compose_C3!$G$13:$G$64,MATCH(F16,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F16,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F16,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F16,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F16,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F16,Compose_C3!$G$15:$G$66,1))+(F16-INDEX(Compose_C3!$G$15:$G$66,MATCH(F16,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F16,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F16,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F16,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F16,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C17,Compose_C3!$A$13:$A$64,1))+(C17-INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C17,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C17,Compose_C3!$A$15:$A$66,1))+(C17-INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C17,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -2756,11 +2756,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C17,Compose_C3!$A$13:$A$64,1))+(C17-INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C17,Compose_C3!$A$15:$A$66,1))+(C17-INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C17,Compose_C3!$A$13:$A$64,1))+(C17-INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C17,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C17,Compose_C3!$A$15:$A$66,1))+(C17-INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C17,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="15">
@@ -2778,11 +2778,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F17,Compose_C3!$G$13:$G$64,1))+(F17-INDEX(Compose_C3!$G$13:$G$64,MATCH(F17,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F17,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F17,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F17,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F17,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F17,Compose_C3!$G$15:$G$66,1))+(F17-INDEX(Compose_C3!$G$15:$G$66,MATCH(F17,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F17,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F17,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F17,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F17,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C18,Compose_C3!$A$13:$A$64,1))+(C18-INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C18,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C18,Compose_C3!$A$15:$A$66,1))+(C18-INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C18,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -2794,11 +2794,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C18,Compose_C3!$A$13:$A$64,1))+(C18-INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C18,Compose_C3!$A$15:$A$66,1))+(C18-INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C18,Compose_C3!$A$13:$A$64,1))+(C18-INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C18,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C18,Compose_C3!$A$15:$A$66,1))+(C18-INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C18,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="15">
@@ -2816,11 +2816,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F18,Compose_C3!$G$13:$G$64,1))+(F18-INDEX(Compose_C3!$G$13:$G$64,MATCH(F18,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F18,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F18,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F18,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F18,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F18,Compose_C3!$G$15:$G$66,1))+(F18-INDEX(Compose_C3!$G$15:$G$66,MATCH(F18,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F18,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F18,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F18,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F18,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C19,Compose_C3!$A$13:$A$64,1))+(C19-INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C19,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C19,Compose_C3!$A$15:$A$66,1))+(C19-INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C19,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -2832,11 +2832,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C19,Compose_C3!$A$13:$A$64,1))+(C19-INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C19,Compose_C3!$A$15:$A$66,1))+(C19-INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C19,Compose_C3!$A$13:$A$64,1))+(C19-INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C19,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C19,Compose_C3!$A$15:$A$66,1))+(C19-INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C19,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="15">
@@ -2854,11 +2854,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F19,Compose_C3!$G$13:$G$64,1))+(F19-INDEX(Compose_C3!$G$13:$G$64,MATCH(F19,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F19,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F19,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F19,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F19,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F19,Compose_C3!$G$15:$G$66,1))+(F19-INDEX(Compose_C3!$G$15:$G$66,MATCH(F19,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F19,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F19,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F19,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F19,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C20,Compose_C3!$A$13:$A$64,1))+(C20-INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C20,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C20,Compose_C3!$A$15:$A$66,1))+(C20-INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C20,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -2870,11 +2870,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C20,Compose_C3!$A$13:$A$64,1))+(C20-INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C20,Compose_C3!$A$15:$A$66,1))+(C20-INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C20,Compose_C3!$A$13:$A$64,1))+(C20-INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C20,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C20,Compose_C3!$A$15:$A$66,1))+(C20-INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C20,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="15">
@@ -2892,11 +2892,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F20,Compose_C3!$G$13:$G$64,1))+(F20-INDEX(Compose_C3!$G$13:$G$64,MATCH(F20,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F20,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F20,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F20,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F20,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F20,Compose_C3!$G$15:$G$66,1))+(F20-INDEX(Compose_C3!$G$15:$G$66,MATCH(F20,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F20,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F20,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F20,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F20,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C21,Compose_C3!$A$13:$A$64,1))+(C21-INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C21,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C21,Compose_C3!$A$15:$A$66,1))+(C21-INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C21,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -2908,11 +2908,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C21,Compose_C3!$A$13:$A$64,1))+(C21-INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C21,Compose_C3!$A$15:$A$66,1))+(C21-INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C21,Compose_C3!$A$13:$A$64,1))+(C21-INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C21,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C21,Compose_C3!$A$15:$A$66,1))+(C21-INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C21,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="15">
@@ -2930,11 +2930,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F21,Compose_C3!$G$13:$G$64,1))+(F21-INDEX(Compose_C3!$G$13:$G$64,MATCH(F21,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F21,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F21,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F21,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F21,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F21,Compose_C3!$G$15:$G$66,1))+(F21-INDEX(Compose_C3!$G$15:$G$66,MATCH(F21,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F21,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F21,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F21,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F21,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C22,Compose_C3!$A$13:$A$64,1))+(C22-INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C22,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C22,Compose_C3!$A$15:$A$66,1))+(C22-INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C22,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -2946,11 +2946,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C22,Compose_C3!$A$13:$A$64,1))+(C22-INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C22,Compose_C3!$A$15:$A$66,1))+(C22-INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C22,Compose_C3!$A$13:$A$64,1))+(C22-INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C22,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C22,Compose_C3!$A$15:$A$66,1))+(C22-INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C22,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="15">
@@ -2968,11 +2968,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F22,Compose_C3!$G$13:$G$64,1))+(F22-INDEX(Compose_C3!$G$13:$G$64,MATCH(F22,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F22,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F22,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F22,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F22,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F22,Compose_C3!$G$15:$G$66,1))+(F22-INDEX(Compose_C3!$G$15:$G$66,MATCH(F22,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F22,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F22,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F22,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F22,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C23,Compose_C3!$A$13:$A$64,1))+(C23-INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C23,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C23,Compose_C3!$A$15:$A$66,1))+(C23-INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C23,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -2984,11 +2984,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C23,Compose_C3!$A$13:$A$64,1))+(C23-INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C23,Compose_C3!$A$15:$A$66,1))+(C23-INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C23,Compose_C3!$A$13:$A$64,1))+(C23-INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C23,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C23,Compose_C3!$A$15:$A$66,1))+(C23-INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C23,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="15">
@@ -3006,11 +3006,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F23,Compose_C3!$G$13:$G$64,1))+(F23-INDEX(Compose_C3!$G$13:$G$64,MATCH(F23,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F23,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F23,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F23,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F23,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F23,Compose_C3!$G$15:$G$66,1))+(F23-INDEX(Compose_C3!$G$15:$G$66,MATCH(F23,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F23,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F23,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F23,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F23,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C24,Compose_C3!$A$13:$A$64,1))+(C24-INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C24,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C24,Compose_C3!$A$15:$A$66,1))+(C24-INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C24,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -3022,11 +3022,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C24,Compose_C3!$A$13:$A$64,1))+(C24-INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C24,Compose_C3!$A$15:$A$66,1))+(C24-INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C24,Compose_C3!$A$13:$A$64,1))+(C24-INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C24,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C24,Compose_C3!$A$15:$A$66,1))+(C24-INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C24,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="15">
@@ -3044,11 +3044,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F24,Compose_C3!$G$13:$G$64,1))+(F24-INDEX(Compose_C3!$G$13:$G$64,MATCH(F24,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F24,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F24,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F24,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F24,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F24,Compose_C3!$G$15:$G$66,1))+(F24-INDEX(Compose_C3!$G$15:$G$66,MATCH(F24,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F24,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F24,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F24,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F24,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C25,Compose_C3!$A$13:$A$64,1))+(C25-INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C25,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C25,Compose_C3!$A$15:$A$66,1))+(C25-INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C25,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -3060,11 +3060,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C25,Compose_C3!$A$13:$A$64,1))+(C25-INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C25,Compose_C3!$A$15:$A$66,1))+(C25-INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C25,Compose_C3!$A$13:$A$64,1))+(C25-INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C25,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C25,Compose_C3!$A$15:$A$66,1))+(C25-INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C25,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="15">
@@ -3082,11 +3082,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F25,Compose_C3!$G$13:$G$64,1))+(F25-INDEX(Compose_C3!$G$13:$G$64,MATCH(F25,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F25,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F25,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F25,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F25,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F25,Compose_C3!$G$15:$G$66,1))+(F25-INDEX(Compose_C3!$G$15:$G$66,MATCH(F25,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F25,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F25,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F25,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F25,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C26,Compose_C3!$A$13:$A$64,1))+(C26-INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C26,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C26,Compose_C3!$A$15:$A$66,1))+(C26-INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C26,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -3098,11 +3098,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C26,Compose_C3!$A$13:$A$64,1))+(C26-INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C26,Compose_C3!$A$15:$A$66,1))+(C26-INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C26,Compose_C3!$A$13:$A$64,1))+(C26-INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C26,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C26,Compose_C3!$A$15:$A$66,1))+(C26-INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C26,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="15">
@@ -3120,11 +3120,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_C3!$G$13:$G$64,1),INDEX(Compose_C3!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_C3!$G$13:$G$64,ROWS(Compose_C3!$G$13:$G$64)),INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$A$13:$A$64,MATCH(F26,Compose_C3!$G$13:$G$64,1))+(F26-INDEX(Compose_C3!$G$13:$G$64,MATCH(F26,Compose_C3!$G$13:$G$64,1)))/(INDEX(Compose_C3!$G$13:$G$64,MATCH(F26,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$G$13:$G$64,MATCH(F26,Compose_C3!$G$13:$G$64,1)))*(INDEX(Compose_C3!$A$13:$A$64,MATCH(F26,Compose_C3!$G$13:$G$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(F26,Compose_C3!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_C3!$G$15:$G$66,1),INDEX(Compose_C3!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_C3!$G$15:$G$66,ROWS(Compose_C3!$G$15:$G$66)),INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$A$15:$A$66,MATCH(F26,Compose_C3!$G$15:$G$66,1))+(F26-INDEX(Compose_C3!$G$15:$G$66,MATCH(F26,Compose_C3!$G$15:$G$66,1)))/(INDEX(Compose_C3!$G$15:$G$66,MATCH(F26,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$G$15:$G$66,MATCH(F26,Compose_C3!$G$15:$G$66,1)))*(INDEX(Compose_C3!$A$15:$A$66,MATCH(F26,Compose_C3!$G$15:$G$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(F26,Compose_C3!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$J$13:$J$64,ROWS(Compose_C3!$J$13:$J$64)),INDEX(Compose_C3!$J$13:$J$64,MATCH(C27,Compose_C3!$A$13:$A$64,1))+(C27-INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$J$13:$J$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$J$13:$J$64,MATCH(C27,Compose_C3!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$J$15:$J$66,ROWS(Compose_C3!$J$15:$J$66)),INDEX(Compose_C3!$J$15:$J$66,MATCH(C27,Compose_C3!$A$15:$A$66,1))+(C27-INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$J$15:$J$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$J$15:$J$66,MATCH(C27,Compose_C3!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -3136,11 +3136,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$H$13:$H$64,ROWS(Compose_C3!$H$13:$H$64)),INDEX(Compose_C3!$H$13:$H$64,MATCH(C27,Compose_C3!$A$13:$A$64,1))+(C27-INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$H$13:$H$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$H$13:$H$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$H$15:$H$66,ROWS(Compose_C3!$H$15:$H$66)),INDEX(Compose_C3!$H$15:$H$66,MATCH(C27,Compose_C3!$A$15:$A$66,1))+(C27-INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$H$15:$H$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$H$15:$H$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C3!$A$13:$A$64,1),INDEX(Compose_C3!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_C3!$A$13:$A$64,ROWS(Compose_C3!$A$13:$A$64)),INDEX(Compose_C3!$I$13:$I$64,ROWS(Compose_C3!$I$13:$I$64)),INDEX(Compose_C3!$I$13:$I$64,MATCH(C27,Compose_C3!$A$13:$A$64,1))+(C27-INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))/(INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$A$13:$A$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))*(INDEX(Compose_C3!$I$13:$I$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)+1)-INDEX(Compose_C3!$I$13:$I$64,MATCH(C27,Compose_C3!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C3!$A$15:$A$66,1),INDEX(Compose_C3!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_C3!$A$15:$A$66,ROWS(Compose_C3!$A$15:$A$66)),INDEX(Compose_C3!$I$15:$I$66,ROWS(Compose_C3!$I$15:$I$66)),INDEX(Compose_C3!$I$15:$I$66,MATCH(C27,Compose_C3!$A$15:$A$66,1))+(C27-INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))/(INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$A$15:$A$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))*(INDEX(Compose_C3!$I$15:$I$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)+1)-INDEX(Compose_C3!$I$15:$I$66,MATCH(C27,Compose_C3!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="15">
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3176,7 +3176,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -3270,142 +3270,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -3432,7 +3362,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -3446,7 +3376,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -3473,7 +3403,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -3487,7 +3417,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -3514,7 +3444,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -3528,7 +3458,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -3555,7 +3485,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -3569,7 +3499,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -3596,7 +3526,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -3610,7 +3540,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -3637,7 +3567,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -3651,7 +3581,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -3678,7 +3608,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -3692,7 +3622,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -3719,7 +3649,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -3733,7 +3663,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -3760,7 +3690,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -3774,7 +3704,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -3801,7 +3731,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -3815,7 +3745,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -3842,7 +3772,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -3856,7 +3786,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -3883,7 +3813,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -3897,7 +3827,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -3924,7 +3854,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -3938,7 +3868,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -3965,7 +3895,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -3979,7 +3909,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -4006,7 +3936,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -4020,7 +3950,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -4047,7 +3977,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -4061,7 +3991,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -4088,7 +4018,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -4102,7 +4032,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -4129,7 +4059,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -4143,7 +4073,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -4170,7 +4100,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -4184,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -4211,7 +4141,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -4225,7 +4155,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -4252,7 +4182,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -4266,7 +4196,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -4293,7 +4223,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -4307,7 +4237,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -4334,7 +4264,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -4348,7 +4278,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -4375,7 +4305,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -4389,7 +4319,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -4416,7 +4346,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -4430,7 +4360,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -4457,7 +4387,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -4471,7 +4401,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -4498,7 +4428,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -4512,7 +4442,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -4539,7 +4469,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -4553,7 +4483,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -4580,7 +4510,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -4594,7 +4524,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -4621,7 +4551,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -4635,7 +4565,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -4662,7 +4592,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -4676,7 +4606,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -4703,7 +4633,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -4717,7 +4647,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -4744,7 +4674,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -4758,7 +4688,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -4785,7 +4715,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -4799,7 +4729,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -4826,7 +4756,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -4840,7 +4770,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -4867,7 +4797,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -4881,7 +4811,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -4908,7 +4838,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -4922,7 +4852,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -4949,7 +4879,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -4963,7 +4893,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -4990,7 +4920,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -5004,7 +4934,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -5031,7 +4961,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -5045,7 +4975,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -5072,7 +5002,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -5086,7 +5016,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -5113,7 +5043,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -5127,7 +5057,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -5154,7 +5084,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -5168,7 +5098,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -5195,7 +5125,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -5209,7 +5139,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -5236,7 +5166,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -5250,7 +5180,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -5277,7 +5207,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -5291,7 +5221,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -5318,7 +5248,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -5332,7 +5262,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -5359,7 +5289,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -5373,7 +5303,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -5400,7 +5330,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -5414,7 +5344,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -5441,7 +5371,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -5450,6 +5380,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
@@ -5686,11 +5698,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F15,Compose_C4!$G$13:$G$64,1))+(F15-INDEX(Compose_C4!$G$13:$G$64,MATCH(F15,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F15,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F15,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F15,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F15,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F15,Compose_C4!$G$15:$G$66,1))+(F15-INDEX(Compose_C4!$G$15:$G$66,MATCH(F15,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F15,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F15,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F15,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F15,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C16,Compose_C4!$A$13:$A$64,1))+(C16-INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C16,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C16,Compose_C4!$A$15:$A$66,1))+(C16-INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C16,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -5702,11 +5714,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C16,Compose_C4!$A$13:$A$64,1))+(C16-INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C16,Compose_C4!$A$15:$A$66,1))+(C16-INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C16,Compose_C4!$A$13:$A$64,1))+(C16-INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C16,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C16,Compose_C4!$A$15:$A$66,1))+(C16-INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C16,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="15">
@@ -5724,11 +5736,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F16,Compose_C4!$G$13:$G$64,1))+(F16-INDEX(Compose_C4!$G$13:$G$64,MATCH(F16,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F16,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F16,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F16,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F16,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F16,Compose_C4!$G$15:$G$66,1))+(F16-INDEX(Compose_C4!$G$15:$G$66,MATCH(F16,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F16,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F16,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F16,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F16,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C17,Compose_C4!$A$13:$A$64,1))+(C17-INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C17,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C17,Compose_C4!$A$15:$A$66,1))+(C17-INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C17,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -5740,11 +5752,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C17,Compose_C4!$A$13:$A$64,1))+(C17-INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C17,Compose_C4!$A$15:$A$66,1))+(C17-INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C17,Compose_C4!$A$13:$A$64,1))+(C17-INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C17,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C17,Compose_C4!$A$15:$A$66,1))+(C17-INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C17,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="15">
@@ -5762,11 +5774,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F17,Compose_C4!$G$13:$G$64,1))+(F17-INDEX(Compose_C4!$G$13:$G$64,MATCH(F17,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F17,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F17,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F17,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F17,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F17,Compose_C4!$G$15:$G$66,1))+(F17-INDEX(Compose_C4!$G$15:$G$66,MATCH(F17,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F17,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F17,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F17,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F17,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C18,Compose_C4!$A$13:$A$64,1))+(C18-INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C18,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C18,Compose_C4!$A$15:$A$66,1))+(C18-INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C18,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -5778,11 +5790,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C18,Compose_C4!$A$13:$A$64,1))+(C18-INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C18,Compose_C4!$A$15:$A$66,1))+(C18-INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C18,Compose_C4!$A$13:$A$64,1))+(C18-INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C18,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C18,Compose_C4!$A$15:$A$66,1))+(C18-INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C18,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="15">
@@ -5800,11 +5812,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F18,Compose_C4!$G$13:$G$64,1))+(F18-INDEX(Compose_C4!$G$13:$G$64,MATCH(F18,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F18,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F18,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F18,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F18,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F18,Compose_C4!$G$15:$G$66,1))+(F18-INDEX(Compose_C4!$G$15:$G$66,MATCH(F18,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F18,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F18,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F18,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F18,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C19,Compose_C4!$A$13:$A$64,1))+(C19-INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C19,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C19,Compose_C4!$A$15:$A$66,1))+(C19-INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C19,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -5816,11 +5828,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C19,Compose_C4!$A$13:$A$64,1))+(C19-INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C19,Compose_C4!$A$15:$A$66,1))+(C19-INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C19,Compose_C4!$A$13:$A$64,1))+(C19-INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C19,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C19,Compose_C4!$A$15:$A$66,1))+(C19-INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C19,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="15">
@@ -5838,11 +5850,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F19,Compose_C4!$G$13:$G$64,1))+(F19-INDEX(Compose_C4!$G$13:$G$64,MATCH(F19,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F19,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F19,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F19,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F19,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F19,Compose_C4!$G$15:$G$66,1))+(F19-INDEX(Compose_C4!$G$15:$G$66,MATCH(F19,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F19,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F19,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F19,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F19,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C20,Compose_C4!$A$13:$A$64,1))+(C20-INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C20,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C20,Compose_C4!$A$15:$A$66,1))+(C20-INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C20,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -5854,11 +5866,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C20,Compose_C4!$A$13:$A$64,1))+(C20-INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C20,Compose_C4!$A$15:$A$66,1))+(C20-INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C20,Compose_C4!$A$13:$A$64,1))+(C20-INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C20,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C20,Compose_C4!$A$15:$A$66,1))+(C20-INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C20,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="15">
@@ -5876,11 +5888,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F20,Compose_C4!$G$13:$G$64,1))+(F20-INDEX(Compose_C4!$G$13:$G$64,MATCH(F20,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F20,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F20,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F20,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F20,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F20,Compose_C4!$G$15:$G$66,1))+(F20-INDEX(Compose_C4!$G$15:$G$66,MATCH(F20,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F20,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F20,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F20,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F20,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C21,Compose_C4!$A$13:$A$64,1))+(C21-INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C21,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C21,Compose_C4!$A$15:$A$66,1))+(C21-INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C21,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -5892,11 +5904,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C21,Compose_C4!$A$13:$A$64,1))+(C21-INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C21,Compose_C4!$A$15:$A$66,1))+(C21-INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C21,Compose_C4!$A$13:$A$64,1))+(C21-INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C21,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C21,Compose_C4!$A$15:$A$66,1))+(C21-INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C21,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="15">
@@ -5914,11 +5926,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F21,Compose_C4!$G$13:$G$64,1))+(F21-INDEX(Compose_C4!$G$13:$G$64,MATCH(F21,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F21,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F21,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F21,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F21,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F21,Compose_C4!$G$15:$G$66,1))+(F21-INDEX(Compose_C4!$G$15:$G$66,MATCH(F21,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F21,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F21,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F21,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F21,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C22,Compose_C4!$A$13:$A$64,1))+(C22-INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C22,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C22,Compose_C4!$A$15:$A$66,1))+(C22-INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C22,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -5930,11 +5942,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C22,Compose_C4!$A$13:$A$64,1))+(C22-INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C22,Compose_C4!$A$15:$A$66,1))+(C22-INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C22,Compose_C4!$A$13:$A$64,1))+(C22-INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C22,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C22,Compose_C4!$A$15:$A$66,1))+(C22-INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C22,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="15">
@@ -5952,11 +5964,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F22,Compose_C4!$G$13:$G$64,1))+(F22-INDEX(Compose_C4!$G$13:$G$64,MATCH(F22,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F22,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F22,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F22,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F22,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F22,Compose_C4!$G$15:$G$66,1))+(F22-INDEX(Compose_C4!$G$15:$G$66,MATCH(F22,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F22,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F22,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F22,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F22,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C23,Compose_C4!$A$13:$A$64,1))+(C23-INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C23,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C23,Compose_C4!$A$15:$A$66,1))+(C23-INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C23,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -5968,11 +5980,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C23,Compose_C4!$A$13:$A$64,1))+(C23-INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C23,Compose_C4!$A$15:$A$66,1))+(C23-INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C23,Compose_C4!$A$13:$A$64,1))+(C23-INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C23,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C23,Compose_C4!$A$15:$A$66,1))+(C23-INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C23,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="15">
@@ -5990,11 +6002,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F23,Compose_C4!$G$13:$G$64,1))+(F23-INDEX(Compose_C4!$G$13:$G$64,MATCH(F23,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F23,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F23,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F23,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F23,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F23,Compose_C4!$G$15:$G$66,1))+(F23-INDEX(Compose_C4!$G$15:$G$66,MATCH(F23,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F23,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F23,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F23,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F23,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C24,Compose_C4!$A$13:$A$64,1))+(C24-INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C24,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C24,Compose_C4!$A$15:$A$66,1))+(C24-INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C24,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -6006,11 +6018,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C24,Compose_C4!$A$13:$A$64,1))+(C24-INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C24,Compose_C4!$A$15:$A$66,1))+(C24-INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C24,Compose_C4!$A$13:$A$64,1))+(C24-INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C24,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C24,Compose_C4!$A$15:$A$66,1))+(C24-INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C24,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="15">
@@ -6028,11 +6040,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F24,Compose_C4!$G$13:$G$64,1))+(F24-INDEX(Compose_C4!$G$13:$G$64,MATCH(F24,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F24,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F24,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F24,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F24,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F24,Compose_C4!$G$15:$G$66,1))+(F24-INDEX(Compose_C4!$G$15:$G$66,MATCH(F24,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F24,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F24,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F24,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F24,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C25,Compose_C4!$A$13:$A$64,1))+(C25-INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C25,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C25,Compose_C4!$A$15:$A$66,1))+(C25-INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C25,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -6044,11 +6056,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C25,Compose_C4!$A$13:$A$64,1))+(C25-INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C25,Compose_C4!$A$15:$A$66,1))+(C25-INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C25,Compose_C4!$A$13:$A$64,1))+(C25-INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C25,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C25,Compose_C4!$A$15:$A$66,1))+(C25-INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C25,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="15">
@@ -6066,11 +6078,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F25,Compose_C4!$G$13:$G$64,1))+(F25-INDEX(Compose_C4!$G$13:$G$64,MATCH(F25,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F25,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F25,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F25,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F25,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F25,Compose_C4!$G$15:$G$66,1))+(F25-INDEX(Compose_C4!$G$15:$G$66,MATCH(F25,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F25,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F25,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F25,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F25,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C26,Compose_C4!$A$13:$A$64,1))+(C26-INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C26,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C26,Compose_C4!$A$15:$A$66,1))+(C26-INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C26,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -6082,11 +6094,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C26,Compose_C4!$A$13:$A$64,1))+(C26-INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C26,Compose_C4!$A$15:$A$66,1))+(C26-INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C26,Compose_C4!$A$13:$A$64,1))+(C26-INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C26,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C26,Compose_C4!$A$15:$A$66,1))+(C26-INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C26,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="15">
@@ -6104,11 +6116,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_C4!$G$13:$G$64,1),INDEX(Compose_C4!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_C4!$G$13:$G$64,ROWS(Compose_C4!$G$13:$G$64)),INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$A$13:$A$64,MATCH(F26,Compose_C4!$G$13:$G$64,1))+(F26-INDEX(Compose_C4!$G$13:$G$64,MATCH(F26,Compose_C4!$G$13:$G$64,1)))/(INDEX(Compose_C4!$G$13:$G$64,MATCH(F26,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$G$13:$G$64,MATCH(F26,Compose_C4!$G$13:$G$64,1)))*(INDEX(Compose_C4!$A$13:$A$64,MATCH(F26,Compose_C4!$G$13:$G$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(F26,Compose_C4!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_C4!$G$15:$G$66,1),INDEX(Compose_C4!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_C4!$G$15:$G$66,ROWS(Compose_C4!$G$15:$G$66)),INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$A$15:$A$66,MATCH(F26,Compose_C4!$G$15:$G$66,1))+(F26-INDEX(Compose_C4!$G$15:$G$66,MATCH(F26,Compose_C4!$G$15:$G$66,1)))/(INDEX(Compose_C4!$G$15:$G$66,MATCH(F26,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$G$15:$G$66,MATCH(F26,Compose_C4!$G$15:$G$66,1)))*(INDEX(Compose_C4!$A$15:$A$66,MATCH(F26,Compose_C4!$G$15:$G$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(F26,Compose_C4!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$J$13:$J$64,ROWS(Compose_C4!$J$13:$J$64)),INDEX(Compose_C4!$J$13:$J$64,MATCH(C27,Compose_C4!$A$13:$A$64,1))+(C27-INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$J$13:$J$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$J$13:$J$64,MATCH(C27,Compose_C4!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$J$15:$J$66,ROWS(Compose_C4!$J$15:$J$66)),INDEX(Compose_C4!$J$15:$J$66,MATCH(C27,Compose_C4!$A$15:$A$66,1))+(C27-INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$J$15:$J$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$J$15:$J$66,MATCH(C27,Compose_C4!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -6120,11 +6132,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$H$13:$H$64,ROWS(Compose_C4!$H$13:$H$64)),INDEX(Compose_C4!$H$13:$H$64,MATCH(C27,Compose_C4!$A$13:$A$64,1))+(C27-INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$H$13:$H$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$H$13:$H$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$H$15:$H$66,ROWS(Compose_C4!$H$15:$H$66)),INDEX(Compose_C4!$H$15:$H$66,MATCH(C27,Compose_C4!$A$15:$A$66,1))+(C27-INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$H$15:$H$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$H$15:$H$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C4!$A$13:$A$64,1),INDEX(Compose_C4!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_C4!$A$13:$A$64,ROWS(Compose_C4!$A$13:$A$64)),INDEX(Compose_C4!$I$13:$I$64,ROWS(Compose_C4!$I$13:$I$64)),INDEX(Compose_C4!$I$13:$I$64,MATCH(C27,Compose_C4!$A$13:$A$64,1))+(C27-INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))/(INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$A$13:$A$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))*(INDEX(Compose_C4!$I$13:$I$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)+1)-INDEX(Compose_C4!$I$13:$I$64,MATCH(C27,Compose_C4!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C4!$A$15:$A$66,1),INDEX(Compose_C4!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_C4!$A$15:$A$66,ROWS(Compose_C4!$A$15:$A$66)),INDEX(Compose_C4!$I$15:$I$66,ROWS(Compose_C4!$I$15:$I$66)),INDEX(Compose_C4!$I$15:$I$66,MATCH(C27,Compose_C4!$A$15:$A$66,1))+(C27-INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))/(INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$A$15:$A$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))*(INDEX(Compose_C4!$I$15:$I$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)+1)-INDEX(Compose_C4!$I$15:$I$66,MATCH(C27,Compose_C4!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="15">
@@ -6147,7 +6159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6160,7 +6172,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -6254,142 +6266,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -6416,7 +6358,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -6430,7 +6372,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -6457,7 +6399,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -6471,7 +6413,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -6498,7 +6440,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -6512,7 +6454,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -6539,7 +6481,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -6553,7 +6495,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -6580,7 +6522,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -6594,7 +6536,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -6621,7 +6563,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -6635,7 +6577,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -6662,7 +6604,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -6676,7 +6618,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -6703,7 +6645,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -6717,7 +6659,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -6744,7 +6686,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -6758,7 +6700,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -6785,7 +6727,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -6799,7 +6741,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -6826,7 +6768,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -6840,7 +6782,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -6867,7 +6809,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -6881,7 +6823,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -6908,7 +6850,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -6922,7 +6864,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -6949,7 +6891,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -6963,7 +6905,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -6990,7 +6932,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -7004,7 +6946,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -7031,7 +6973,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -7045,7 +6987,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -7072,7 +7014,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -7086,7 +7028,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -7113,7 +7055,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -7127,7 +7069,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -7154,7 +7096,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -7168,7 +7110,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -7195,7 +7137,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -7209,7 +7151,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -7236,7 +7178,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -7250,7 +7192,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -7277,7 +7219,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -7291,7 +7233,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -7318,7 +7260,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -7332,7 +7274,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -7359,7 +7301,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -7373,7 +7315,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -7400,7 +7342,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -7414,7 +7356,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -7441,7 +7383,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -7455,7 +7397,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -7482,7 +7424,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -7496,7 +7438,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -7523,7 +7465,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -7537,7 +7479,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -7564,7 +7506,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -7578,7 +7520,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -7605,7 +7547,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -7619,7 +7561,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -7646,7 +7588,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -7660,7 +7602,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -7687,7 +7629,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -7701,7 +7643,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -7728,7 +7670,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -7742,7 +7684,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -7769,7 +7711,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -7783,7 +7725,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -7810,7 +7752,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -7824,7 +7766,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -7851,7 +7793,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -7865,7 +7807,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -7892,7 +7834,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -7906,7 +7848,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -7933,7 +7875,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -7947,7 +7889,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -7974,7 +7916,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -7988,7 +7930,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -8015,7 +7957,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -8029,7 +7971,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -8056,7 +7998,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -8070,7 +8012,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -8097,7 +8039,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -8111,7 +8053,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -8138,7 +8080,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -8152,7 +8094,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -8179,7 +8121,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -8193,7 +8135,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -8220,7 +8162,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -8234,7 +8176,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -8261,7 +8203,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -8275,7 +8217,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -8302,7 +8244,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -8316,7 +8258,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -8343,7 +8285,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -8357,7 +8299,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -8384,7 +8326,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -8398,7 +8340,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -8425,7 +8367,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -8434,6 +8376,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
@@ -8670,11 +8694,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F15,Compose_C5!$G$13:$G$64,1))+(F15-INDEX(Compose_C5!$G$13:$G$64,MATCH(F15,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F15,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F15,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F15,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F15,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F15,Compose_C5!$G$15:$G$66,1))+(F15-INDEX(Compose_C5!$G$15:$G$66,MATCH(F15,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F15,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F15,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F15,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F15,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C16,Compose_C5!$A$13:$A$64,1))+(C16-INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C16,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C16,Compose_C5!$A$15:$A$66,1))+(C16-INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C16,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -8686,11 +8710,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C16,Compose_C5!$A$13:$A$64,1))+(C16-INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C16,Compose_C5!$A$15:$A$66,1))+(C16-INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C16,Compose_C5!$A$13:$A$64,1))+(C16-INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C16,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C16,Compose_C5!$A$15:$A$66,1))+(C16-INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C16,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="15">
@@ -8708,11 +8732,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F16,Compose_C5!$G$13:$G$64,1))+(F16-INDEX(Compose_C5!$G$13:$G$64,MATCH(F16,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F16,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F16,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F16,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F16,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F16,Compose_C5!$G$15:$G$66,1))+(F16-INDEX(Compose_C5!$G$15:$G$66,MATCH(F16,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F16,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F16,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F16,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F16,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C17,Compose_C5!$A$13:$A$64,1))+(C17-INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C17,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C17,Compose_C5!$A$15:$A$66,1))+(C17-INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C17,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -8724,11 +8748,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C17,Compose_C5!$A$13:$A$64,1))+(C17-INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C17,Compose_C5!$A$15:$A$66,1))+(C17-INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C17,Compose_C5!$A$13:$A$64,1))+(C17-INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C17,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C17,Compose_C5!$A$15:$A$66,1))+(C17-INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C17,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="15">
@@ -8746,11 +8770,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F17,Compose_C5!$G$13:$G$64,1))+(F17-INDEX(Compose_C5!$G$13:$G$64,MATCH(F17,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F17,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F17,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F17,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F17,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F17,Compose_C5!$G$15:$G$66,1))+(F17-INDEX(Compose_C5!$G$15:$G$66,MATCH(F17,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F17,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F17,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F17,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F17,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C18,Compose_C5!$A$13:$A$64,1))+(C18-INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C18,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C18,Compose_C5!$A$15:$A$66,1))+(C18-INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C18,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -8762,11 +8786,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C18,Compose_C5!$A$13:$A$64,1))+(C18-INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C18,Compose_C5!$A$15:$A$66,1))+(C18-INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C18,Compose_C5!$A$13:$A$64,1))+(C18-INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C18,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C18,Compose_C5!$A$15:$A$66,1))+(C18-INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C18,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="15">
@@ -8784,11 +8808,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F18,Compose_C5!$G$13:$G$64,1))+(F18-INDEX(Compose_C5!$G$13:$G$64,MATCH(F18,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F18,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F18,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F18,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F18,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F18,Compose_C5!$G$15:$G$66,1))+(F18-INDEX(Compose_C5!$G$15:$G$66,MATCH(F18,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F18,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F18,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F18,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F18,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C19,Compose_C5!$A$13:$A$64,1))+(C19-INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C19,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C19,Compose_C5!$A$15:$A$66,1))+(C19-INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C19,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -8800,11 +8824,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C19,Compose_C5!$A$13:$A$64,1))+(C19-INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C19,Compose_C5!$A$15:$A$66,1))+(C19-INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C19,Compose_C5!$A$13:$A$64,1))+(C19-INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C19,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C19,Compose_C5!$A$15:$A$66,1))+(C19-INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C19,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="15">
@@ -8822,11 +8846,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F19,Compose_C5!$G$13:$G$64,1))+(F19-INDEX(Compose_C5!$G$13:$G$64,MATCH(F19,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F19,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F19,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F19,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F19,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F19,Compose_C5!$G$15:$G$66,1))+(F19-INDEX(Compose_C5!$G$15:$G$66,MATCH(F19,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F19,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F19,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F19,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F19,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C20,Compose_C5!$A$13:$A$64,1))+(C20-INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C20,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C20,Compose_C5!$A$15:$A$66,1))+(C20-INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C20,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -8838,11 +8862,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C20,Compose_C5!$A$13:$A$64,1))+(C20-INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C20,Compose_C5!$A$15:$A$66,1))+(C20-INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C20,Compose_C5!$A$13:$A$64,1))+(C20-INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C20,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C20,Compose_C5!$A$15:$A$66,1))+(C20-INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C20,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="15">
@@ -8860,11 +8884,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F20,Compose_C5!$G$13:$G$64,1))+(F20-INDEX(Compose_C5!$G$13:$G$64,MATCH(F20,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F20,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F20,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F20,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F20,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F20,Compose_C5!$G$15:$G$66,1))+(F20-INDEX(Compose_C5!$G$15:$G$66,MATCH(F20,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F20,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F20,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F20,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F20,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C21,Compose_C5!$A$13:$A$64,1))+(C21-INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C21,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C21,Compose_C5!$A$15:$A$66,1))+(C21-INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C21,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -8876,11 +8900,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C21,Compose_C5!$A$13:$A$64,1))+(C21-INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C21,Compose_C5!$A$15:$A$66,1))+(C21-INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C21,Compose_C5!$A$13:$A$64,1))+(C21-INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C21,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C21,Compose_C5!$A$15:$A$66,1))+(C21-INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C21,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="15">
@@ -8898,11 +8922,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F21,Compose_C5!$G$13:$G$64,1))+(F21-INDEX(Compose_C5!$G$13:$G$64,MATCH(F21,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F21,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F21,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F21,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F21,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F21,Compose_C5!$G$15:$G$66,1))+(F21-INDEX(Compose_C5!$G$15:$G$66,MATCH(F21,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F21,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F21,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F21,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F21,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C22,Compose_C5!$A$13:$A$64,1))+(C22-INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C22,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C22,Compose_C5!$A$15:$A$66,1))+(C22-INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C22,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -8914,11 +8938,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C22,Compose_C5!$A$13:$A$64,1))+(C22-INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C22,Compose_C5!$A$15:$A$66,1))+(C22-INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C22,Compose_C5!$A$13:$A$64,1))+(C22-INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C22,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C22,Compose_C5!$A$15:$A$66,1))+(C22-INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C22,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="15">
@@ -8936,11 +8960,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F22,Compose_C5!$G$13:$G$64,1))+(F22-INDEX(Compose_C5!$G$13:$G$64,MATCH(F22,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F22,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F22,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F22,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F22,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F22,Compose_C5!$G$15:$G$66,1))+(F22-INDEX(Compose_C5!$G$15:$G$66,MATCH(F22,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F22,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F22,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F22,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F22,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C23,Compose_C5!$A$13:$A$64,1))+(C23-INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C23,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C23,Compose_C5!$A$15:$A$66,1))+(C23-INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C23,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -8952,11 +8976,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C23,Compose_C5!$A$13:$A$64,1))+(C23-INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C23,Compose_C5!$A$15:$A$66,1))+(C23-INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C23,Compose_C5!$A$13:$A$64,1))+(C23-INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C23,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C23,Compose_C5!$A$15:$A$66,1))+(C23-INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C23,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="15">
@@ -8974,11 +8998,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F23,Compose_C5!$G$13:$G$64,1))+(F23-INDEX(Compose_C5!$G$13:$G$64,MATCH(F23,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F23,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F23,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F23,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F23,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F23,Compose_C5!$G$15:$G$66,1))+(F23-INDEX(Compose_C5!$G$15:$G$66,MATCH(F23,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F23,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F23,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F23,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F23,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C24,Compose_C5!$A$13:$A$64,1))+(C24-INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C24,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C24,Compose_C5!$A$15:$A$66,1))+(C24-INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C24,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -8990,11 +9014,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C24,Compose_C5!$A$13:$A$64,1))+(C24-INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C24,Compose_C5!$A$15:$A$66,1))+(C24-INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C24,Compose_C5!$A$13:$A$64,1))+(C24-INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C24,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C24,Compose_C5!$A$15:$A$66,1))+(C24-INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C24,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="15">
@@ -9012,11 +9036,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F24,Compose_C5!$G$13:$G$64,1))+(F24-INDEX(Compose_C5!$G$13:$G$64,MATCH(F24,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F24,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F24,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F24,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F24,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F24,Compose_C5!$G$15:$G$66,1))+(F24-INDEX(Compose_C5!$G$15:$G$66,MATCH(F24,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F24,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F24,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F24,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F24,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C25,Compose_C5!$A$13:$A$64,1))+(C25-INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C25,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C25,Compose_C5!$A$15:$A$66,1))+(C25-INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C25,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -9028,11 +9052,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C25,Compose_C5!$A$13:$A$64,1))+(C25-INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C25,Compose_C5!$A$15:$A$66,1))+(C25-INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C25,Compose_C5!$A$13:$A$64,1))+(C25-INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C25,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C25,Compose_C5!$A$15:$A$66,1))+(C25-INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C25,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="15">
@@ -9050,11 +9074,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F25,Compose_C5!$G$13:$G$64,1))+(F25-INDEX(Compose_C5!$G$13:$G$64,MATCH(F25,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F25,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F25,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F25,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F25,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F25,Compose_C5!$G$15:$G$66,1))+(F25-INDEX(Compose_C5!$G$15:$G$66,MATCH(F25,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F25,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F25,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F25,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F25,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C26,Compose_C5!$A$13:$A$64,1))+(C26-INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C26,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C26,Compose_C5!$A$15:$A$66,1))+(C26-INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C26,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -9066,11 +9090,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C26,Compose_C5!$A$13:$A$64,1))+(C26-INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C26,Compose_C5!$A$15:$A$66,1))+(C26-INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C26,Compose_C5!$A$13:$A$64,1))+(C26-INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C26,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C26,Compose_C5!$A$15:$A$66,1))+(C26-INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C26,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="15">
@@ -9088,11 +9112,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_C5!$G$13:$G$64,1),INDEX(Compose_C5!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_C5!$G$13:$G$64,ROWS(Compose_C5!$G$13:$G$64)),INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$A$13:$A$64,MATCH(F26,Compose_C5!$G$13:$G$64,1))+(F26-INDEX(Compose_C5!$G$13:$G$64,MATCH(F26,Compose_C5!$G$13:$G$64,1)))/(INDEX(Compose_C5!$G$13:$G$64,MATCH(F26,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$G$13:$G$64,MATCH(F26,Compose_C5!$G$13:$G$64,1)))*(INDEX(Compose_C5!$A$13:$A$64,MATCH(F26,Compose_C5!$G$13:$G$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(F26,Compose_C5!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_C5!$G$15:$G$66,1),INDEX(Compose_C5!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_C5!$G$15:$G$66,ROWS(Compose_C5!$G$15:$G$66)),INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$A$15:$A$66,MATCH(F26,Compose_C5!$G$15:$G$66,1))+(F26-INDEX(Compose_C5!$G$15:$G$66,MATCH(F26,Compose_C5!$G$15:$G$66,1)))/(INDEX(Compose_C5!$G$15:$G$66,MATCH(F26,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$G$15:$G$66,MATCH(F26,Compose_C5!$G$15:$G$66,1)))*(INDEX(Compose_C5!$A$15:$A$66,MATCH(F26,Compose_C5!$G$15:$G$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(F26,Compose_C5!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$J$13:$J$64,ROWS(Compose_C5!$J$13:$J$64)),INDEX(Compose_C5!$J$13:$J$64,MATCH(C27,Compose_C5!$A$13:$A$64,1))+(C27-INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$J$13:$J$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$J$13:$J$64,MATCH(C27,Compose_C5!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$J$15:$J$66,ROWS(Compose_C5!$J$15:$J$66)),INDEX(Compose_C5!$J$15:$J$66,MATCH(C27,Compose_C5!$A$15:$A$66,1))+(C27-INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$J$15:$J$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$J$15:$J$66,MATCH(C27,Compose_C5!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -9104,11 +9128,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$H$13:$H$64,ROWS(Compose_C5!$H$13:$H$64)),INDEX(Compose_C5!$H$13:$H$64,MATCH(C27,Compose_C5!$A$13:$A$64,1))+(C27-INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$H$13:$H$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$H$13:$H$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$H$15:$H$66,ROWS(Compose_C5!$H$15:$H$66)),INDEX(Compose_C5!$H$15:$H$66,MATCH(C27,Compose_C5!$A$15:$A$66,1))+(C27-INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$H$15:$H$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$H$15:$H$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C5!$A$13:$A$64,1),INDEX(Compose_C5!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_C5!$A$13:$A$64,ROWS(Compose_C5!$A$13:$A$64)),INDEX(Compose_C5!$I$13:$I$64,ROWS(Compose_C5!$I$13:$I$64)),INDEX(Compose_C5!$I$13:$I$64,MATCH(C27,Compose_C5!$A$13:$A$64,1))+(C27-INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))/(INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$A$13:$A$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))*(INDEX(Compose_C5!$I$13:$I$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)+1)-INDEX(Compose_C5!$I$13:$I$64,MATCH(C27,Compose_C5!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C5!$A$15:$A$66,1),INDEX(Compose_C5!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_C5!$A$15:$A$66,ROWS(Compose_C5!$A$15:$A$66)),INDEX(Compose_C5!$I$15:$I$66,ROWS(Compose_C5!$I$15:$I$66)),INDEX(Compose_C5!$I$15:$I$66,MATCH(C27,Compose_C5!$A$15:$A$66,1))+(C27-INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))/(INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$A$15:$A$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))*(INDEX(Compose_C5!$I$15:$I$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)+1)-INDEX(Compose_C5!$I$15:$I$66,MATCH(C27,Compose_C5!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="15">
@@ -9131,7 +9155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9144,7 +9168,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -9238,142 +9262,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -9400,7 +9354,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -9414,7 +9368,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -9441,7 +9395,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -9455,7 +9409,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -9482,7 +9436,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -9496,7 +9450,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -9523,7 +9477,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -9537,7 +9491,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -9564,7 +9518,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -9578,7 +9532,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -9605,7 +9559,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -9619,7 +9573,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -9646,7 +9600,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -9660,7 +9614,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -9687,7 +9641,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -9701,7 +9655,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -9728,7 +9682,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -9742,7 +9696,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -9769,7 +9723,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -9783,7 +9737,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -9810,7 +9764,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -9824,7 +9778,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -9851,7 +9805,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -9865,7 +9819,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -9892,7 +9846,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -9906,7 +9860,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -9933,7 +9887,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -9947,7 +9901,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -9974,7 +9928,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -9988,7 +9942,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -10015,7 +9969,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -10029,7 +9983,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -10056,7 +10010,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -10070,7 +10024,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -10097,7 +10051,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -10111,7 +10065,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -10138,7 +10092,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -10152,7 +10106,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -10179,7 +10133,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -10193,7 +10147,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -10220,7 +10174,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -10234,7 +10188,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -10261,7 +10215,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -10275,7 +10229,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -10302,7 +10256,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -10316,7 +10270,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -10343,7 +10297,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -10357,7 +10311,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -10384,7 +10338,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -10398,7 +10352,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -10425,7 +10379,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -10439,7 +10393,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -10466,7 +10420,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -10480,7 +10434,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -10507,7 +10461,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -10521,7 +10475,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -10548,7 +10502,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -10562,7 +10516,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -10589,7 +10543,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -10603,7 +10557,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -10630,7 +10584,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -10644,7 +10598,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -10671,7 +10625,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -10685,7 +10639,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -10712,7 +10666,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -10726,7 +10680,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -10753,7 +10707,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -10767,7 +10721,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -10794,7 +10748,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -10808,7 +10762,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -10835,7 +10789,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -10849,7 +10803,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -10876,7 +10830,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -10890,7 +10844,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -10917,7 +10871,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -10931,7 +10885,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -10958,7 +10912,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -10972,7 +10926,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -10999,7 +10953,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -11013,7 +10967,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -11040,7 +10994,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -11054,7 +11008,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -11081,7 +11035,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -11095,7 +11049,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -11122,7 +11076,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -11136,7 +11090,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -11163,7 +11117,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -11177,7 +11131,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -11204,7 +11158,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -11218,7 +11172,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -11245,7 +11199,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -11259,7 +11213,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -11286,7 +11240,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -11300,7 +11254,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -11327,7 +11281,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -11341,7 +11295,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -11368,7 +11322,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -11382,7 +11336,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -11409,7 +11363,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -11418,6 +11372,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
@@ -11654,11 +11690,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F15,Compose_C6!$G$13:$G$64,1))+(F15-INDEX(Compose_C6!$G$13:$G$64,MATCH(F15,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F15,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F15,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F15,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F15,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F15,Compose_C6!$G$15:$G$66,1))+(F15-INDEX(Compose_C6!$G$15:$G$66,MATCH(F15,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F15,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F15,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F15,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F15,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C16,Compose_C6!$A$13:$A$64,1))+(C16-INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C16,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C16,Compose_C6!$A$15:$A$66,1))+(C16-INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C16,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -11670,11 +11706,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C16,Compose_C6!$A$13:$A$64,1))+(C16-INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C16,Compose_C6!$A$15:$A$66,1))+(C16-INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C16,Compose_C6!$A$13:$A$64,1))+(C16-INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C16,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C16,Compose_C6!$A$15:$A$66,1))+(C16-INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C16,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="15">
@@ -11692,11 +11728,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F16,Compose_C6!$G$13:$G$64,1))+(F16-INDEX(Compose_C6!$G$13:$G$64,MATCH(F16,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F16,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F16,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F16,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F16,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F16,Compose_C6!$G$15:$G$66,1))+(F16-INDEX(Compose_C6!$G$15:$G$66,MATCH(F16,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F16,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F16,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F16,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F16,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C17,Compose_C6!$A$13:$A$64,1))+(C17-INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C17,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C17,Compose_C6!$A$15:$A$66,1))+(C17-INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C17,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -11708,11 +11744,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C17,Compose_C6!$A$13:$A$64,1))+(C17-INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C17,Compose_C6!$A$15:$A$66,1))+(C17-INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C17,Compose_C6!$A$13:$A$64,1))+(C17-INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C17,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C17,Compose_C6!$A$15:$A$66,1))+(C17-INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C17,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="15">
@@ -11730,11 +11766,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F17,Compose_C6!$G$13:$G$64,1))+(F17-INDEX(Compose_C6!$G$13:$G$64,MATCH(F17,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F17,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F17,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F17,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F17,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F17,Compose_C6!$G$15:$G$66,1))+(F17-INDEX(Compose_C6!$G$15:$G$66,MATCH(F17,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F17,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F17,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F17,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F17,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C18,Compose_C6!$A$13:$A$64,1))+(C18-INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C18,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C18,Compose_C6!$A$15:$A$66,1))+(C18-INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C18,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -11746,11 +11782,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C18,Compose_C6!$A$13:$A$64,1))+(C18-INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C18,Compose_C6!$A$15:$A$66,1))+(C18-INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C18,Compose_C6!$A$13:$A$64,1))+(C18-INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C18,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C18,Compose_C6!$A$15:$A$66,1))+(C18-INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C18,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="15">
@@ -11768,11 +11804,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F18,Compose_C6!$G$13:$G$64,1))+(F18-INDEX(Compose_C6!$G$13:$G$64,MATCH(F18,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F18,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F18,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F18,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F18,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F18,Compose_C6!$G$15:$G$66,1))+(F18-INDEX(Compose_C6!$G$15:$G$66,MATCH(F18,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F18,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F18,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F18,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F18,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C19,Compose_C6!$A$13:$A$64,1))+(C19-INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C19,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C19,Compose_C6!$A$15:$A$66,1))+(C19-INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C19,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -11784,11 +11820,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C19,Compose_C6!$A$13:$A$64,1))+(C19-INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C19,Compose_C6!$A$15:$A$66,1))+(C19-INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C19,Compose_C6!$A$13:$A$64,1))+(C19-INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C19,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C19,Compose_C6!$A$15:$A$66,1))+(C19-INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C19,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="15">
@@ -11806,11 +11842,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F19,Compose_C6!$G$13:$G$64,1))+(F19-INDEX(Compose_C6!$G$13:$G$64,MATCH(F19,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F19,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F19,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F19,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F19,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F19,Compose_C6!$G$15:$G$66,1))+(F19-INDEX(Compose_C6!$G$15:$G$66,MATCH(F19,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F19,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F19,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F19,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F19,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C20,Compose_C6!$A$13:$A$64,1))+(C20-INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C20,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C20,Compose_C6!$A$15:$A$66,1))+(C20-INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C20,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -11822,11 +11858,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C20,Compose_C6!$A$13:$A$64,1))+(C20-INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C20,Compose_C6!$A$15:$A$66,1))+(C20-INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C20,Compose_C6!$A$13:$A$64,1))+(C20-INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C20,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C20,Compose_C6!$A$15:$A$66,1))+(C20-INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C20,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="15">
@@ -11844,11 +11880,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F20,Compose_C6!$G$13:$G$64,1))+(F20-INDEX(Compose_C6!$G$13:$G$64,MATCH(F20,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F20,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F20,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F20,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F20,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F20,Compose_C6!$G$15:$G$66,1))+(F20-INDEX(Compose_C6!$G$15:$G$66,MATCH(F20,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F20,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F20,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F20,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F20,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C21,Compose_C6!$A$13:$A$64,1))+(C21-INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C21,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C21,Compose_C6!$A$15:$A$66,1))+(C21-INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C21,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -11860,11 +11896,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C21,Compose_C6!$A$13:$A$64,1))+(C21-INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C21,Compose_C6!$A$15:$A$66,1))+(C21-INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C21,Compose_C6!$A$13:$A$64,1))+(C21-INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C21,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C21,Compose_C6!$A$15:$A$66,1))+(C21-INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C21,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="15">
@@ -11882,11 +11918,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F21,Compose_C6!$G$13:$G$64,1))+(F21-INDEX(Compose_C6!$G$13:$G$64,MATCH(F21,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F21,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F21,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F21,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F21,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F21,Compose_C6!$G$15:$G$66,1))+(F21-INDEX(Compose_C6!$G$15:$G$66,MATCH(F21,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F21,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F21,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F21,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F21,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C22,Compose_C6!$A$13:$A$64,1))+(C22-INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C22,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C22,Compose_C6!$A$15:$A$66,1))+(C22-INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C22,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -11898,11 +11934,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C22,Compose_C6!$A$13:$A$64,1))+(C22-INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C22,Compose_C6!$A$15:$A$66,1))+(C22-INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C22,Compose_C6!$A$13:$A$64,1))+(C22-INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C22,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C22,Compose_C6!$A$15:$A$66,1))+(C22-INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C22,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="15">
@@ -11920,11 +11956,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F22,Compose_C6!$G$13:$G$64,1))+(F22-INDEX(Compose_C6!$G$13:$G$64,MATCH(F22,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F22,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F22,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F22,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F22,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F22,Compose_C6!$G$15:$G$66,1))+(F22-INDEX(Compose_C6!$G$15:$G$66,MATCH(F22,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F22,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F22,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F22,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F22,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C23,Compose_C6!$A$13:$A$64,1))+(C23-INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C23,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C23,Compose_C6!$A$15:$A$66,1))+(C23-INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C23,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -11936,11 +11972,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C23,Compose_C6!$A$13:$A$64,1))+(C23-INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C23,Compose_C6!$A$15:$A$66,1))+(C23-INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C23,Compose_C6!$A$13:$A$64,1))+(C23-INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C23,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C23,Compose_C6!$A$15:$A$66,1))+(C23-INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C23,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="15">
@@ -11958,11 +11994,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F23,Compose_C6!$G$13:$G$64,1))+(F23-INDEX(Compose_C6!$G$13:$G$64,MATCH(F23,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F23,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F23,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F23,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F23,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F23,Compose_C6!$G$15:$G$66,1))+(F23-INDEX(Compose_C6!$G$15:$G$66,MATCH(F23,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F23,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F23,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F23,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F23,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C24,Compose_C6!$A$13:$A$64,1))+(C24-INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C24,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C24,Compose_C6!$A$15:$A$66,1))+(C24-INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C24,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -11974,11 +12010,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C24,Compose_C6!$A$13:$A$64,1))+(C24-INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C24,Compose_C6!$A$15:$A$66,1))+(C24-INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C24,Compose_C6!$A$13:$A$64,1))+(C24-INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C24,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C24,Compose_C6!$A$15:$A$66,1))+(C24-INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C24,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="15">
@@ -11996,11 +12032,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F24,Compose_C6!$G$13:$G$64,1))+(F24-INDEX(Compose_C6!$G$13:$G$64,MATCH(F24,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F24,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F24,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F24,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F24,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F24,Compose_C6!$G$15:$G$66,1))+(F24-INDEX(Compose_C6!$G$15:$G$66,MATCH(F24,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F24,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F24,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F24,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F24,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C25,Compose_C6!$A$13:$A$64,1))+(C25-INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C25,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C25,Compose_C6!$A$15:$A$66,1))+(C25-INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C25,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -12012,11 +12048,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C25,Compose_C6!$A$13:$A$64,1))+(C25-INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C25,Compose_C6!$A$15:$A$66,1))+(C25-INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C25,Compose_C6!$A$13:$A$64,1))+(C25-INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C25,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C25,Compose_C6!$A$15:$A$66,1))+(C25-INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C25,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="15">
@@ -12034,11 +12070,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F25,Compose_C6!$G$13:$G$64,1))+(F25-INDEX(Compose_C6!$G$13:$G$64,MATCH(F25,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F25,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F25,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F25,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F25,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F25,Compose_C6!$G$15:$G$66,1))+(F25-INDEX(Compose_C6!$G$15:$G$66,MATCH(F25,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F25,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F25,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F25,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F25,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C26,Compose_C6!$A$13:$A$64,1))+(C26-INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C26,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C26,Compose_C6!$A$15:$A$66,1))+(C26-INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C26,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -12050,11 +12086,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C26,Compose_C6!$A$13:$A$64,1))+(C26-INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C26,Compose_C6!$A$15:$A$66,1))+(C26-INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C26,Compose_C6!$A$13:$A$64,1))+(C26-INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C26,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C26,Compose_C6!$A$15:$A$66,1))+(C26-INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C26,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="15">
@@ -12072,11 +12108,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_C6!$G$13:$G$64,1),INDEX(Compose_C6!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_C6!$G$13:$G$64,ROWS(Compose_C6!$G$13:$G$64)),INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$A$13:$A$64,MATCH(F26,Compose_C6!$G$13:$G$64,1))+(F26-INDEX(Compose_C6!$G$13:$G$64,MATCH(F26,Compose_C6!$G$13:$G$64,1)))/(INDEX(Compose_C6!$G$13:$G$64,MATCH(F26,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$G$13:$G$64,MATCH(F26,Compose_C6!$G$13:$G$64,1)))*(INDEX(Compose_C6!$A$13:$A$64,MATCH(F26,Compose_C6!$G$13:$G$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(F26,Compose_C6!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_C6!$G$15:$G$66,1),INDEX(Compose_C6!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_C6!$G$15:$G$66,ROWS(Compose_C6!$G$15:$G$66)),INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$A$15:$A$66,MATCH(F26,Compose_C6!$G$15:$G$66,1))+(F26-INDEX(Compose_C6!$G$15:$G$66,MATCH(F26,Compose_C6!$G$15:$G$66,1)))/(INDEX(Compose_C6!$G$15:$G$66,MATCH(F26,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$G$15:$G$66,MATCH(F26,Compose_C6!$G$15:$G$66,1)))*(INDEX(Compose_C6!$A$15:$A$66,MATCH(F26,Compose_C6!$G$15:$G$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(F26,Compose_C6!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$J$13:$J$64,ROWS(Compose_C6!$J$13:$J$64)),INDEX(Compose_C6!$J$13:$J$64,MATCH(C27,Compose_C6!$A$13:$A$64,1))+(C27-INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$J$13:$J$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$J$13:$J$64,MATCH(C27,Compose_C6!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$J$15:$J$66,ROWS(Compose_C6!$J$15:$J$66)),INDEX(Compose_C6!$J$15:$J$66,MATCH(C27,Compose_C6!$A$15:$A$66,1))+(C27-INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$J$15:$J$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$J$15:$J$66,MATCH(C27,Compose_C6!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -12088,11 +12124,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$H$13:$H$64,ROWS(Compose_C6!$H$13:$H$64)),INDEX(Compose_C6!$H$13:$H$64,MATCH(C27,Compose_C6!$A$13:$A$64,1))+(C27-INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$H$13:$H$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$H$13:$H$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$H$15:$H$66,ROWS(Compose_C6!$H$15:$H$66)),INDEX(Compose_C6!$H$15:$H$66,MATCH(C27,Compose_C6!$A$15:$A$66,1))+(C27-INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$H$15:$H$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$H$15:$H$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C6!$A$13:$A$64,1),INDEX(Compose_C6!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_C6!$A$13:$A$64,ROWS(Compose_C6!$A$13:$A$64)),INDEX(Compose_C6!$I$13:$I$64,ROWS(Compose_C6!$I$13:$I$64)),INDEX(Compose_C6!$I$13:$I$64,MATCH(C27,Compose_C6!$A$13:$A$64,1))+(C27-INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))/(INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$A$13:$A$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))*(INDEX(Compose_C6!$I$13:$I$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)+1)-INDEX(Compose_C6!$I$13:$I$64,MATCH(C27,Compose_C6!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C6!$A$15:$A$66,1),INDEX(Compose_C6!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_C6!$A$15:$A$66,ROWS(Compose_C6!$A$15:$A$66)),INDEX(Compose_C6!$I$15:$I$66,ROWS(Compose_C6!$I$15:$I$66)),INDEX(Compose_C6!$I$15:$I$66,MATCH(C27,Compose_C6!$A$15:$A$66,1))+(C27-INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))/(INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$A$15:$A$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))*(INDEX(Compose_C6!$I$15:$I$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)+1)-INDEX(Compose_C6!$I$15:$I$66,MATCH(C27,Compose_C6!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="15">
@@ -14217,7 +14253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14230,7 +14266,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -14324,142 +14360,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -14486,7 +14452,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -14500,7 +14466,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -14527,7 +14493,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -14541,7 +14507,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -14568,7 +14534,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -14582,7 +14548,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -14609,7 +14575,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -14623,7 +14589,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -14650,7 +14616,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -14664,7 +14630,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -14691,7 +14657,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -14705,7 +14671,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -14732,7 +14698,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -14746,7 +14712,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -14773,7 +14739,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -14787,7 +14753,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -14814,7 +14780,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -14828,7 +14794,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -14855,7 +14821,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -14869,7 +14835,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -14896,7 +14862,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -14910,7 +14876,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -14937,7 +14903,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -14951,7 +14917,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -14978,7 +14944,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -14992,7 +14958,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -15019,7 +14985,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -15033,7 +14999,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -15060,7 +15026,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -15074,7 +15040,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -15101,7 +15067,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -15115,7 +15081,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -15142,7 +15108,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -15156,7 +15122,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -15183,7 +15149,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -15197,7 +15163,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -15224,7 +15190,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -15238,7 +15204,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -15265,7 +15231,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -15279,7 +15245,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -15306,7 +15272,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -15320,7 +15286,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -15347,7 +15313,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -15361,7 +15327,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -15388,7 +15354,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -15402,7 +15368,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -15429,7 +15395,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -15443,7 +15409,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -15470,7 +15436,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -15484,7 +15450,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -15511,7 +15477,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -15525,7 +15491,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -15552,7 +15518,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -15566,7 +15532,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -15593,7 +15559,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -15607,7 +15573,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -15634,7 +15600,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -15648,7 +15614,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -15675,7 +15641,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -15689,7 +15655,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -15716,7 +15682,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -15730,7 +15696,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -15757,7 +15723,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -15771,7 +15737,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -15798,7 +15764,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -15812,7 +15778,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -15839,7 +15805,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -15853,7 +15819,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -15880,7 +15846,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -15894,7 +15860,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -15921,7 +15887,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -15935,7 +15901,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -15962,7 +15928,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -15976,7 +15942,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -16003,7 +15969,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -16017,7 +15983,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -16044,7 +16010,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -16058,7 +16024,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -16085,7 +16051,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -16099,7 +16065,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -16126,7 +16092,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -16140,7 +16106,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -16167,7 +16133,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -16181,7 +16147,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -16208,7 +16174,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -16222,7 +16188,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -16249,7 +16215,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -16263,7 +16229,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -16290,7 +16256,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -16304,7 +16270,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -16331,7 +16297,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -16345,7 +16311,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -16372,7 +16338,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -16386,7 +16352,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -16413,7 +16379,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -16427,7 +16393,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -16454,7 +16420,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -16468,7 +16434,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -16495,7 +16461,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -16504,6 +16470,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
@@ -16740,11 +16788,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F15,Compose_C1!$G$13:$G$64,1))+(F15-INDEX(Compose_C1!$G$13:$G$64,MATCH(F15,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F15,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F15,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F15,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F15,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F15,Compose_C1!$G$15:$G$66,1))+(F15-INDEX(Compose_C1!$G$15:$G$66,MATCH(F15,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F15,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F15,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F15,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F15,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C16,Compose_C1!$A$13:$A$64,1))+(C16-INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C16,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C16,Compose_C1!$A$15:$A$66,1))+(C16-INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C16,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -16756,11 +16804,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C16,Compose_C1!$A$13:$A$64,1))+(C16-INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C16,Compose_C1!$A$15:$A$66,1))+(C16-INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C16,Compose_C1!$A$13:$A$64,1))+(C16-INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C16,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C16,Compose_C1!$A$15:$A$66,1))+(C16-INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C16,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="15">
@@ -16778,11 +16826,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F16,Compose_C1!$G$13:$G$64,1))+(F16-INDEX(Compose_C1!$G$13:$G$64,MATCH(F16,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F16,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F16,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F16,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F16,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F16,Compose_C1!$G$15:$G$66,1))+(F16-INDEX(Compose_C1!$G$15:$G$66,MATCH(F16,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F16,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F16,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F16,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F16,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C17,Compose_C1!$A$13:$A$64,1))+(C17-INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C17,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C17,Compose_C1!$A$15:$A$66,1))+(C17-INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C17,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -16794,11 +16842,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C17,Compose_C1!$A$13:$A$64,1))+(C17-INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C17,Compose_C1!$A$15:$A$66,1))+(C17-INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C17,Compose_C1!$A$13:$A$64,1))+(C17-INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C17,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C17,Compose_C1!$A$15:$A$66,1))+(C17-INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C17,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="15">
@@ -16816,11 +16864,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F17,Compose_C1!$G$13:$G$64,1))+(F17-INDEX(Compose_C1!$G$13:$G$64,MATCH(F17,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F17,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F17,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F17,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F17,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F17,Compose_C1!$G$15:$G$66,1))+(F17-INDEX(Compose_C1!$G$15:$G$66,MATCH(F17,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F17,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F17,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F17,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F17,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C18,Compose_C1!$A$13:$A$64,1))+(C18-INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C18,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C18,Compose_C1!$A$15:$A$66,1))+(C18-INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C18,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -16832,11 +16880,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C18,Compose_C1!$A$13:$A$64,1))+(C18-INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C18,Compose_C1!$A$15:$A$66,1))+(C18-INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C18,Compose_C1!$A$13:$A$64,1))+(C18-INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C18,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C18,Compose_C1!$A$15:$A$66,1))+(C18-INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C18,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="15">
@@ -16854,11 +16902,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F18,Compose_C1!$G$13:$G$64,1))+(F18-INDEX(Compose_C1!$G$13:$G$64,MATCH(F18,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F18,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F18,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F18,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F18,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F18,Compose_C1!$G$15:$G$66,1))+(F18-INDEX(Compose_C1!$G$15:$G$66,MATCH(F18,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F18,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F18,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F18,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F18,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C19,Compose_C1!$A$13:$A$64,1))+(C19-INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C19,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C19,Compose_C1!$A$15:$A$66,1))+(C19-INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C19,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -16870,11 +16918,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C19,Compose_C1!$A$13:$A$64,1))+(C19-INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C19,Compose_C1!$A$15:$A$66,1))+(C19-INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C19,Compose_C1!$A$13:$A$64,1))+(C19-INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C19,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C19,Compose_C1!$A$15:$A$66,1))+(C19-INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C19,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="15">
@@ -16892,11 +16940,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F19,Compose_C1!$G$13:$G$64,1))+(F19-INDEX(Compose_C1!$G$13:$G$64,MATCH(F19,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F19,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F19,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F19,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F19,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F19,Compose_C1!$G$15:$G$66,1))+(F19-INDEX(Compose_C1!$G$15:$G$66,MATCH(F19,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F19,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F19,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F19,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F19,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C20,Compose_C1!$A$13:$A$64,1))+(C20-INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C20,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C20,Compose_C1!$A$15:$A$66,1))+(C20-INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C20,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -16908,11 +16956,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C20,Compose_C1!$A$13:$A$64,1))+(C20-INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C20,Compose_C1!$A$15:$A$66,1))+(C20-INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C20,Compose_C1!$A$13:$A$64,1))+(C20-INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C20,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C20,Compose_C1!$A$15:$A$66,1))+(C20-INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C20,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="15">
@@ -16930,11 +16978,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F20,Compose_C1!$G$13:$G$64,1))+(F20-INDEX(Compose_C1!$G$13:$G$64,MATCH(F20,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F20,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F20,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F20,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F20,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F20,Compose_C1!$G$15:$G$66,1))+(F20-INDEX(Compose_C1!$G$15:$G$66,MATCH(F20,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F20,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F20,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F20,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F20,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C21,Compose_C1!$A$13:$A$64,1))+(C21-INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C21,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C21,Compose_C1!$A$15:$A$66,1))+(C21-INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C21,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -16946,11 +16994,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C21,Compose_C1!$A$13:$A$64,1))+(C21-INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C21,Compose_C1!$A$15:$A$66,1))+(C21-INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C21,Compose_C1!$A$13:$A$64,1))+(C21-INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C21,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C21,Compose_C1!$A$15:$A$66,1))+(C21-INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C21,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="15">
@@ -16968,11 +17016,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F21,Compose_C1!$G$13:$G$64,1))+(F21-INDEX(Compose_C1!$G$13:$G$64,MATCH(F21,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F21,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F21,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F21,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F21,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F21,Compose_C1!$G$15:$G$66,1))+(F21-INDEX(Compose_C1!$G$15:$G$66,MATCH(F21,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F21,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F21,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F21,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F21,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C22,Compose_C1!$A$13:$A$64,1))+(C22-INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C22,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C22,Compose_C1!$A$15:$A$66,1))+(C22-INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C22,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -16984,11 +17032,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C22,Compose_C1!$A$13:$A$64,1))+(C22-INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C22,Compose_C1!$A$15:$A$66,1))+(C22-INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C22,Compose_C1!$A$13:$A$64,1))+(C22-INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C22,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C22,Compose_C1!$A$15:$A$66,1))+(C22-INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C22,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="15">
@@ -17006,11 +17054,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F22,Compose_C1!$G$13:$G$64,1))+(F22-INDEX(Compose_C1!$G$13:$G$64,MATCH(F22,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F22,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F22,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F22,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F22,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F22,Compose_C1!$G$15:$G$66,1))+(F22-INDEX(Compose_C1!$G$15:$G$66,MATCH(F22,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F22,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F22,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F22,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F22,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C23,Compose_C1!$A$13:$A$64,1))+(C23-INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C23,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C23,Compose_C1!$A$15:$A$66,1))+(C23-INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C23,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -17022,11 +17070,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C23,Compose_C1!$A$13:$A$64,1))+(C23-INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C23,Compose_C1!$A$15:$A$66,1))+(C23-INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C23,Compose_C1!$A$13:$A$64,1))+(C23-INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C23,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C23,Compose_C1!$A$15:$A$66,1))+(C23-INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C23,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="15">
@@ -17044,11 +17092,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F23,Compose_C1!$G$13:$G$64,1))+(F23-INDEX(Compose_C1!$G$13:$G$64,MATCH(F23,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F23,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F23,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F23,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F23,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F23,Compose_C1!$G$15:$G$66,1))+(F23-INDEX(Compose_C1!$G$15:$G$66,MATCH(F23,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F23,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F23,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F23,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F23,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C24,Compose_C1!$A$13:$A$64,1))+(C24-INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C24,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C24,Compose_C1!$A$15:$A$66,1))+(C24-INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C24,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -17060,11 +17108,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C24,Compose_C1!$A$13:$A$64,1))+(C24-INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C24,Compose_C1!$A$15:$A$66,1))+(C24-INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C24,Compose_C1!$A$13:$A$64,1))+(C24-INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C24,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C24,Compose_C1!$A$15:$A$66,1))+(C24-INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C24,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="15">
@@ -17082,11 +17130,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F24,Compose_C1!$G$13:$G$64,1))+(F24-INDEX(Compose_C1!$G$13:$G$64,MATCH(F24,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F24,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F24,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F24,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F24,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F24,Compose_C1!$G$15:$G$66,1))+(F24-INDEX(Compose_C1!$G$15:$G$66,MATCH(F24,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F24,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F24,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F24,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F24,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C25,Compose_C1!$A$13:$A$64,1))+(C25-INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C25,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C25,Compose_C1!$A$15:$A$66,1))+(C25-INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C25,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -17098,11 +17146,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C25,Compose_C1!$A$13:$A$64,1))+(C25-INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C25,Compose_C1!$A$15:$A$66,1))+(C25-INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C25,Compose_C1!$A$13:$A$64,1))+(C25-INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C25,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C25,Compose_C1!$A$15:$A$66,1))+(C25-INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C25,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="15">
@@ -17120,11 +17168,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F25,Compose_C1!$G$13:$G$64,1))+(F25-INDEX(Compose_C1!$G$13:$G$64,MATCH(F25,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F25,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F25,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F25,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F25,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F25,Compose_C1!$G$15:$G$66,1))+(F25-INDEX(Compose_C1!$G$15:$G$66,MATCH(F25,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F25,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F25,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F25,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F25,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C26,Compose_C1!$A$13:$A$64,1))+(C26-INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C26,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C26,Compose_C1!$A$15:$A$66,1))+(C26-INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C26,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -17136,11 +17184,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C26,Compose_C1!$A$13:$A$64,1))+(C26-INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C26,Compose_C1!$A$15:$A$66,1))+(C26-INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C26,Compose_C1!$A$13:$A$64,1))+(C26-INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C26,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C26,Compose_C1!$A$15:$A$66,1))+(C26-INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C26,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="15">
@@ -17158,11 +17206,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_C1!$G$13:$G$64,1),INDEX(Compose_C1!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_C1!$G$13:$G$64,ROWS(Compose_C1!$G$13:$G$64)),INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$A$13:$A$64,MATCH(F26,Compose_C1!$G$13:$G$64,1))+(F26-INDEX(Compose_C1!$G$13:$G$64,MATCH(F26,Compose_C1!$G$13:$G$64,1)))/(INDEX(Compose_C1!$G$13:$G$64,MATCH(F26,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$G$13:$G$64,MATCH(F26,Compose_C1!$G$13:$G$64,1)))*(INDEX(Compose_C1!$A$13:$A$64,MATCH(F26,Compose_C1!$G$13:$G$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(F26,Compose_C1!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_C1!$G$15:$G$66,1),INDEX(Compose_C1!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_C1!$G$15:$G$66,ROWS(Compose_C1!$G$15:$G$66)),INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$A$15:$A$66,MATCH(F26,Compose_C1!$G$15:$G$66,1))+(F26-INDEX(Compose_C1!$G$15:$G$66,MATCH(F26,Compose_C1!$G$15:$G$66,1)))/(INDEX(Compose_C1!$G$15:$G$66,MATCH(F26,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$G$15:$G$66,MATCH(F26,Compose_C1!$G$15:$G$66,1)))*(INDEX(Compose_C1!$A$15:$A$66,MATCH(F26,Compose_C1!$G$15:$G$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(F26,Compose_C1!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$J$13:$J$64,ROWS(Compose_C1!$J$13:$J$64)),INDEX(Compose_C1!$J$13:$J$64,MATCH(C27,Compose_C1!$A$13:$A$64,1))+(C27-INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$J$13:$J$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$J$13:$J$64,MATCH(C27,Compose_C1!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$J$15:$J$66,ROWS(Compose_C1!$J$15:$J$66)),INDEX(Compose_C1!$J$15:$J$66,MATCH(C27,Compose_C1!$A$15:$A$66,1))+(C27-INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$J$15:$J$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$J$15:$J$66,MATCH(C27,Compose_C1!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -17174,11 +17222,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$H$13:$H$64,ROWS(Compose_C1!$H$13:$H$64)),INDEX(Compose_C1!$H$13:$H$64,MATCH(C27,Compose_C1!$A$13:$A$64,1))+(C27-INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$H$13:$H$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$H$13:$H$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$H$15:$H$66,ROWS(Compose_C1!$H$15:$H$66)),INDEX(Compose_C1!$H$15:$H$66,MATCH(C27,Compose_C1!$A$15:$A$66,1))+(C27-INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$H$15:$H$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$H$15:$H$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C1!$A$13:$A$64,1),INDEX(Compose_C1!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_C1!$A$13:$A$64,ROWS(Compose_C1!$A$13:$A$64)),INDEX(Compose_C1!$I$13:$I$64,ROWS(Compose_C1!$I$13:$I$64)),INDEX(Compose_C1!$I$13:$I$64,MATCH(C27,Compose_C1!$A$13:$A$64,1))+(C27-INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))/(INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$A$13:$A$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))*(INDEX(Compose_C1!$I$13:$I$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)+1)-INDEX(Compose_C1!$I$13:$I$64,MATCH(C27,Compose_C1!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C1!$A$15:$A$66,1),INDEX(Compose_C1!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_C1!$A$15:$A$66,ROWS(Compose_C1!$A$15:$A$66)),INDEX(Compose_C1!$I$15:$I$66,ROWS(Compose_C1!$I$15:$I$66)),INDEX(Compose_C1!$I$15:$I$66,MATCH(C27,Compose_C1!$A$15:$A$66,1))+(C27-INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))/(INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$A$15:$A$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))*(INDEX(Compose_C1!$I$15:$I$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)+1)-INDEX(Compose_C1!$I$15:$I$66,MATCH(C27,Compose_C1!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="15">
@@ -17201,7 +17249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17214,7 +17262,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -17308,142 +17356,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -17470,7 +17448,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -17484,7 +17462,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -17511,7 +17489,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -17525,7 +17503,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -17552,7 +17530,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -17566,7 +17544,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -17593,7 +17571,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -17607,7 +17585,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -17634,7 +17612,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -17648,7 +17626,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -17675,7 +17653,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -17689,7 +17667,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -17716,7 +17694,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -17730,7 +17708,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -17757,7 +17735,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -17771,7 +17749,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -17798,7 +17776,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -17812,7 +17790,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -17839,7 +17817,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -17853,7 +17831,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -17880,7 +17858,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -17894,7 +17872,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -17921,7 +17899,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -17935,7 +17913,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -17962,7 +17940,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -17976,7 +17954,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -18003,7 +17981,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -18017,7 +17995,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -18044,7 +18022,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -18058,7 +18036,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -18085,7 +18063,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -18099,7 +18077,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -18126,7 +18104,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -18140,7 +18118,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -18167,7 +18145,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -18181,7 +18159,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -18208,7 +18186,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -18222,7 +18200,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -18249,7 +18227,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -18263,7 +18241,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -18290,7 +18268,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -18304,7 +18282,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -18331,7 +18309,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -18345,7 +18323,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -18372,7 +18350,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -18386,7 +18364,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -18413,7 +18391,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -18427,7 +18405,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -18454,7 +18432,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -18468,7 +18446,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -18495,7 +18473,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -18509,7 +18487,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -18536,7 +18514,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -18550,7 +18528,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -18577,7 +18555,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -18591,7 +18569,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -18618,7 +18596,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -18632,7 +18610,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -18659,7 +18637,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -18673,7 +18651,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -18700,7 +18678,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -18714,7 +18692,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -18741,7 +18719,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -18755,7 +18733,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -18782,7 +18760,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -18796,7 +18774,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -18823,7 +18801,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -18837,7 +18815,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -18864,7 +18842,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -18878,7 +18856,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -18905,7 +18883,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -18919,7 +18897,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -18946,7 +18924,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -18960,7 +18938,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -18987,7 +18965,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -19001,7 +18979,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -19028,7 +19006,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -19042,7 +19020,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -19069,7 +19047,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -19083,7 +19061,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -19110,7 +19088,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -19124,7 +19102,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -19151,7 +19129,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -19165,7 +19143,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -19192,7 +19170,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -19206,7 +19184,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -19233,7 +19211,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -19247,7 +19225,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -19274,7 +19252,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -19288,7 +19266,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -19315,7 +19293,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -19329,7 +19307,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -19356,7 +19334,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -19370,7 +19348,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -19397,7 +19375,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -19411,7 +19389,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -19438,7 +19416,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -19452,7 +19430,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -19479,7 +19457,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -19488,6 +19466,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
@@ -19724,11 +19784,11 @@
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IF(F15&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F15&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F15,Compose_C2!$G$13:$G$64,1))+(F15-INDEX(Compose_C2!$G$13:$G$64,MATCH(F15,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F15,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F15,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F15,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F15,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F15&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F15&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F15,Compose_C2!$G$15:$G$66,1))+(F15-INDEX(Compose_C2!$G$15:$G$66,MATCH(F15,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F15,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F15,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F15,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F15,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C16&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C16,Compose_C2!$A$13:$A$64,1))+(C16-INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C16,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F15&lt;=0.01,MIN(0.5*(B15+B16),$B$4),IF(C16&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C16&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C16,Compose_C2!$A$15:$A$66,1))+(C16-INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C16,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E16" s="16">
@@ -19740,11 +19800,11 @@
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C16&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C16,Compose_C2!$A$13:$A$64,1))+(C16-INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C16&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C16,Compose_C2!$A$15:$A$66,1))+(C16-INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>IF(C16&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C16&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C16,Compose_C2!$A$13:$A$64,1))+(C16-INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C16,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C16&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C16&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C16,Compose_C2!$A$15:$A$66,1))+(C16-INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C16,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I16" s="15">
@@ -19762,11 +19822,11 @@
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IF(F16&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F16&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F16,Compose_C2!$G$13:$G$64,1))+(F16-INDEX(Compose_C2!$G$13:$G$64,MATCH(F16,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F16,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F16,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F16,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F16,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F16&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F16&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F16,Compose_C2!$G$15:$G$66,1))+(F16-INDEX(Compose_C2!$G$15:$G$66,MATCH(F16,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F16,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F16,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F16,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F16,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C17&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C17,Compose_C2!$A$13:$A$64,1))+(C17-INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C17,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F16&lt;=0.01,MIN(0.5*(B16+B17),$B$4),IF(C17&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C17&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C17,Compose_C2!$A$15:$A$66,1))+(C17-INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C17,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E17" s="16">
@@ -19778,11 +19838,11 @@
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C17&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C17,Compose_C2!$A$13:$A$64,1))+(C17-INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C17&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C17,Compose_C2!$A$15:$A$66,1))+(C17-INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>IF(C17&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C17&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C17,Compose_C2!$A$13:$A$64,1))+(C17-INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C17,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C17&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C17&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C17,Compose_C2!$A$15:$A$66,1))+(C17-INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C17,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I17" s="15">
@@ -19800,11 +19860,11 @@
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IF(F17&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F17&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F17,Compose_C2!$G$13:$G$64,1))+(F17-INDEX(Compose_C2!$G$13:$G$64,MATCH(F17,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F17,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F17,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F17,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F17,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F17&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F17&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F17,Compose_C2!$G$15:$G$66,1))+(F17-INDEX(Compose_C2!$G$15:$G$66,MATCH(F17,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F17,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F17,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F17,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F17,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C18&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C18,Compose_C2!$A$13:$A$64,1))+(C18-INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C18,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F17&lt;=0.01,MIN(0.5*(B17+B18),$B$4),IF(C18&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C18&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C18,Compose_C2!$A$15:$A$66,1))+(C18-INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C18,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E18" s="16">
@@ -19816,11 +19876,11 @@
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C18&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C18,Compose_C2!$A$13:$A$64,1))+(C18-INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C18&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C18,Compose_C2!$A$15:$A$66,1))+(C18-INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>IF(C18&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C18&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C18,Compose_C2!$A$13:$A$64,1))+(C18-INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C18,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C18&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C18&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C18,Compose_C2!$A$15:$A$66,1))+(C18-INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C18,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I18" s="15">
@@ -19838,11 +19898,11 @@
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IF(F18&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F18&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F18,Compose_C2!$G$13:$G$64,1))+(F18-INDEX(Compose_C2!$G$13:$G$64,MATCH(F18,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F18,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F18,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F18,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F18,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F18&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F18&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F18,Compose_C2!$G$15:$G$66,1))+(F18-INDEX(Compose_C2!$G$15:$G$66,MATCH(F18,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F18,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F18,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F18,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F18,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C19&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C19,Compose_C2!$A$13:$A$64,1))+(C19-INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C19,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F18&lt;=0.01,MIN(0.5*(B18+B19),$B$4),IF(C19&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C19&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C19,Compose_C2!$A$15:$A$66,1))+(C19-INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C19,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E19" s="16">
@@ -19854,11 +19914,11 @@
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C19&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C19,Compose_C2!$A$13:$A$64,1))+(C19-INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C19&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C19,Compose_C2!$A$15:$A$66,1))+(C19-INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>IF(C19&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C19&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C19,Compose_C2!$A$13:$A$64,1))+(C19-INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C19,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C19&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C19&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C19,Compose_C2!$A$15:$A$66,1))+(C19-INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C19,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I19" s="15">
@@ -19876,11 +19936,11 @@
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IF(F19&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F19&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F19,Compose_C2!$G$13:$G$64,1))+(F19-INDEX(Compose_C2!$G$13:$G$64,MATCH(F19,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F19,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F19,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F19,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F19,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F19&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F19&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F19,Compose_C2!$G$15:$G$66,1))+(F19-INDEX(Compose_C2!$G$15:$G$66,MATCH(F19,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F19,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F19,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F19,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F19,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C20&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C20,Compose_C2!$A$13:$A$64,1))+(C20-INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C20,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F19&lt;=0.01,MIN(0.5*(B19+B20),$B$4),IF(C20&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C20&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C20,Compose_C2!$A$15:$A$66,1))+(C20-INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C20,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E20" s="16">
@@ -19892,11 +19952,11 @@
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C20&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C20,Compose_C2!$A$13:$A$64,1))+(C20-INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C20&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C20,Compose_C2!$A$15:$A$66,1))+(C20-INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>IF(C20&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C20&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C20,Compose_C2!$A$13:$A$64,1))+(C20-INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C20,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C20&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C20&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C20,Compose_C2!$A$15:$A$66,1))+(C20-INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C20,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I20" s="15">
@@ -19914,11 +19974,11 @@
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IF(F20&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F20&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F20,Compose_C2!$G$13:$G$64,1))+(F20-INDEX(Compose_C2!$G$13:$G$64,MATCH(F20,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F20,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F20,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F20,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F20,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F20&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F20&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F20,Compose_C2!$G$15:$G$66,1))+(F20-INDEX(Compose_C2!$G$15:$G$66,MATCH(F20,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F20,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F20,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F20,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F20,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C21&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C21,Compose_C2!$A$13:$A$64,1))+(C21-INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C21,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F20&lt;=0.01,MIN(0.5*(B20+B21),$B$4),IF(C21&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C21&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C21,Compose_C2!$A$15:$A$66,1))+(C21-INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C21,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E21" s="16">
@@ -19930,11 +19990,11 @@
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C21&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C21,Compose_C2!$A$13:$A$64,1))+(C21-INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C21&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C21,Compose_C2!$A$15:$A$66,1))+(C21-INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>IF(C21&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C21&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C21,Compose_C2!$A$13:$A$64,1))+(C21-INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C21,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C21&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C21&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C21,Compose_C2!$A$15:$A$66,1))+(C21-INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C21,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I21" s="15">
@@ -19952,11 +20012,11 @@
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IF(F21&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F21&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F21,Compose_C2!$G$13:$G$64,1))+(F21-INDEX(Compose_C2!$G$13:$G$64,MATCH(F21,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F21,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F21,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F21,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F21,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F21&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F21&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F21,Compose_C2!$G$15:$G$66,1))+(F21-INDEX(Compose_C2!$G$15:$G$66,MATCH(F21,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F21,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F21,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F21,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F21,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C22&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C22,Compose_C2!$A$13:$A$64,1))+(C22-INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C22,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F21&lt;=0.01,MIN(0.5*(B21+B22),$B$4),IF(C22&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C22&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C22,Compose_C2!$A$15:$A$66,1))+(C22-INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C22,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E22" s="16">
@@ -19968,11 +20028,11 @@
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C22&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C22,Compose_C2!$A$13:$A$64,1))+(C22-INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C22&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C22,Compose_C2!$A$15:$A$66,1))+(C22-INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>IF(C22&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C22&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C22,Compose_C2!$A$13:$A$64,1))+(C22-INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C22,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C22&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C22&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C22,Compose_C2!$A$15:$A$66,1))+(C22-INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C22,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I22" s="15">
@@ -19990,11 +20050,11 @@
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IF(F22&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F22&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F22,Compose_C2!$G$13:$G$64,1))+(F22-INDEX(Compose_C2!$G$13:$G$64,MATCH(F22,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F22,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F22,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F22,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F22,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F22&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F22&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F22,Compose_C2!$G$15:$G$66,1))+(F22-INDEX(Compose_C2!$G$15:$G$66,MATCH(F22,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F22,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F22,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F22,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F22,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C23&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C23,Compose_C2!$A$13:$A$64,1))+(C23-INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C23,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F22&lt;=0.01,MIN(0.5*(B22+B23),$B$4),IF(C23&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C23&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C23,Compose_C2!$A$15:$A$66,1))+(C23-INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C23,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E23" s="16">
@@ -20006,11 +20066,11 @@
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C23&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C23,Compose_C2!$A$13:$A$64,1))+(C23-INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C23&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C23,Compose_C2!$A$15:$A$66,1))+(C23-INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>IF(C23&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C23&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C23,Compose_C2!$A$13:$A$64,1))+(C23-INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C23,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C23&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C23&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C23,Compose_C2!$A$15:$A$66,1))+(C23-INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C23,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I23" s="15">
@@ -20028,11 +20088,11 @@
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IF(F23&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F23&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F23,Compose_C2!$G$13:$G$64,1))+(F23-INDEX(Compose_C2!$G$13:$G$64,MATCH(F23,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F23,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F23,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F23,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F23,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F23&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F23&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F23,Compose_C2!$G$15:$G$66,1))+(F23-INDEX(Compose_C2!$G$15:$G$66,MATCH(F23,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F23,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F23,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F23,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F23,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C24&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C24,Compose_C2!$A$13:$A$64,1))+(C24-INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C24,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F23&lt;=0.01,MIN(0.5*(B23+B24),$B$4),IF(C24&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C24&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C24,Compose_C2!$A$15:$A$66,1))+(C24-INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C24,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -20044,11 +20104,11 @@
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C24&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C24,Compose_C2!$A$13:$A$64,1))+(C24-INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C24&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C24,Compose_C2!$A$15:$A$66,1))+(C24-INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>IF(C24&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C24&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C24,Compose_C2!$A$13:$A$64,1))+(C24-INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C24,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C24&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C24&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C24,Compose_C2!$A$15:$A$66,1))+(C24-INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C24,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I24" s="15">
@@ -20066,11 +20126,11 @@
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IF(F24&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F24&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F24,Compose_C2!$G$13:$G$64,1))+(F24-INDEX(Compose_C2!$G$13:$G$64,MATCH(F24,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F24,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F24,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F24,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F24,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F24&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F24&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F24,Compose_C2!$G$15:$G$66,1))+(F24-INDEX(Compose_C2!$G$15:$G$66,MATCH(F24,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F24,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F24,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F24,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F24,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C25&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C25,Compose_C2!$A$13:$A$64,1))+(C25-INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C25,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F24&lt;=0.01,MIN(0.5*(B24+B25),$B$4),IF(C25&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C25&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C25,Compose_C2!$A$15:$A$66,1))+(C25-INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C25,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -20082,11 +20142,11 @@
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C25&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C25,Compose_C2!$A$13:$A$64,1))+(C25-INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C25&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C25,Compose_C2!$A$15:$A$66,1))+(C25-INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>IF(C25&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C25&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C25,Compose_C2!$A$13:$A$64,1))+(C25-INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C25,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C25&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C25&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C25,Compose_C2!$A$15:$A$66,1))+(C25-INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C25,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I25" s="15">
@@ -20104,11 +20164,11 @@
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IF(F25&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F25&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F25,Compose_C2!$G$13:$G$64,1))+(F25-INDEX(Compose_C2!$G$13:$G$64,MATCH(F25,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F25,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F25,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F25,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F25,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F25&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F25&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F25,Compose_C2!$G$15:$G$66,1))+(F25-INDEX(Compose_C2!$G$15:$G$66,MATCH(F25,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F25,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F25,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F25,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F25,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C26&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C26,Compose_C2!$A$13:$A$64,1))+(C26-INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C26,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F25&lt;=0.01,MIN(0.5*(B25+B26),$B$4),IF(C26&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C26&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C26,Compose_C2!$A$15:$A$66,1))+(C26-INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C26,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E26" s="16">
@@ -20120,11 +20180,11 @@
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C26&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C26,Compose_C2!$A$13:$A$64,1))+(C26-INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C26&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C26,Compose_C2!$A$15:$A$66,1))+(C26-INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>IF(C26&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C26&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C26,Compose_C2!$A$13:$A$64,1))+(C26-INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C26,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C26&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C26&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C26,Compose_C2!$A$15:$A$66,1))+(C26-INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C26,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I26" s="15">
@@ -20142,11 +20202,11 @@
         <v/>
       </c>
       <c r="C27" s="17">
-        <f>IF(F26&lt;=INDEX(Compose_C2!$G$13:$G$64,1),INDEX(Compose_C2!$A$13:$A$64,1),IF(F26&gt;=INDEX(Compose_C2!$G$13:$G$64,ROWS(Compose_C2!$G$13:$G$64)),INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$A$13:$A$64,MATCH(F26,Compose_C2!$G$13:$G$64,1))+(F26-INDEX(Compose_C2!$G$13:$G$64,MATCH(F26,Compose_C2!$G$13:$G$64,1)))/(INDEX(Compose_C2!$G$13:$G$64,MATCH(F26,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$G$13:$G$64,MATCH(F26,Compose_C2!$G$13:$G$64,1)))*(INDEX(Compose_C2!$A$13:$A$64,MATCH(F26,Compose_C2!$G$13:$G$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(F26,Compose_C2!$G$13:$G$64,1)))))</f>
+        <f>IF(F26&lt;=INDEX(Compose_C2!$G$15:$G$66,1),INDEX(Compose_C2!$A$15:$A$66,1),IF(F26&gt;=INDEX(Compose_C2!$G$15:$G$66,ROWS(Compose_C2!$G$15:$G$66)),INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$A$15:$A$66,MATCH(F26,Compose_C2!$G$15:$G$66,1))+(F26-INDEX(Compose_C2!$G$15:$G$66,MATCH(F26,Compose_C2!$G$15:$G$66,1)))/(INDEX(Compose_C2!$G$15:$G$66,MATCH(F26,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$G$15:$G$66,MATCH(F26,Compose_C2!$G$15:$G$66,1)))*(INDEX(Compose_C2!$A$15:$A$66,MATCH(F26,Compose_C2!$G$15:$G$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(F26,Compose_C2!$G$15:$G$66,1)))))</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$J$13:$J$64,1),IF(C27&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$J$13:$J$64,ROWS(Compose_C2!$J$13:$J$64)),INDEX(Compose_C2!$J$13:$J$64,MATCH(C27,Compose_C2!$A$13:$A$64,1))+(C27-INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$J$13:$J$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$J$13:$J$64,MATCH(C27,Compose_C2!$A$13:$A$64,1))))))</f>
+        <f>IF(F26&lt;=0.01,MIN(0.5*(B26+B27),$B$4),IF(C27&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$J$15:$J$66,1),IF(C27&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$J$15:$J$66,ROWS(Compose_C2!$J$15:$J$66)),INDEX(Compose_C2!$J$15:$J$66,MATCH(C27,Compose_C2!$A$15:$A$66,1))+(C27-INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$J$15:$J$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$J$15:$J$66,MATCH(C27,Compose_C2!$A$15:$A$66,1))))))</f>
         <v/>
       </c>
       <c r="E27" s="16">
@@ -20158,11 +20218,11 @@
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$H$13:$H$64,1),IF(C27&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$H$13:$H$64,ROWS(Compose_C2!$H$13:$H$64)),INDEX(Compose_C2!$H$13:$H$64,MATCH(C27,Compose_C2!$A$13:$A$64,1))+(C27-INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$H$13:$H$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$H$13:$H$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$H$15:$H$66,1),IF(C27&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$H$15:$H$66,ROWS(Compose_C2!$H$15:$H$66)),INDEX(Compose_C2!$H$15:$H$66,MATCH(C27,Compose_C2!$A$15:$A$66,1))+(C27-INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$H$15:$H$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$H$15:$H$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>IF(C27&lt;=INDEX(Compose_C2!$A$13:$A$64,1),INDEX(Compose_C2!$I$13:$I$64,1),IF(C27&gt;=INDEX(Compose_C2!$A$13:$A$64,ROWS(Compose_C2!$A$13:$A$64)),INDEX(Compose_C2!$I$13:$I$64,ROWS(Compose_C2!$I$13:$I$64)),INDEX(Compose_C2!$I$13:$I$64,MATCH(C27,Compose_C2!$A$13:$A$64,1))+(C27-INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))/(INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$A$13:$A$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))*(INDEX(Compose_C2!$I$13:$I$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)+1)-INDEX(Compose_C2!$I$13:$I$64,MATCH(C27,Compose_C2!$A$13:$A$64,1)))))</f>
+        <f>IF(C27&lt;=INDEX(Compose_C2!$A$15:$A$66,1),INDEX(Compose_C2!$I$15:$I$66,1),IF(C27&gt;=INDEX(Compose_C2!$A$15:$A$66,ROWS(Compose_C2!$A$15:$A$66)),INDEX(Compose_C2!$I$15:$I$66,ROWS(Compose_C2!$I$15:$I$66)),INDEX(Compose_C2!$I$15:$I$66,MATCH(C27,Compose_C2!$A$15:$A$66,1))+(C27-INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))/(INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$A$15:$A$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))*(INDEX(Compose_C2!$I$15:$I$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)+1)-INDEX(Compose_C2!$I$15:$I$66,MATCH(C27,Compose_C2!$A$15:$A$66,1)))))</f>
         <v/>
       </c>
       <c r="I27" s="15">
@@ -20185,7 +20245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20198,7 +20258,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colonnes = formules Excel. Crest / facteur pipe en jaune.</t>
+          <t>Colonnes = formules Excel. Crest / facteur pipe / plafond Q en jaune.</t>
         </is>
       </c>
     </row>
@@ -20292,142 +20352,72 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q_cap (m3/s)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HW</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>y_ov</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>A_ditch</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>V_ditch</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>V_pond</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>V_total</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Q_1200</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>Q_overflow</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>Qout</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="B13" s="19">
-        <f>A13-$B$10</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>MAX(0,A13-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(C13&lt;=0,0,($B$5+$B$7*C13)*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>D13*$B$9</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>IF(A13&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A13&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1))+(A13-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A13,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G13" s="13">
-        <f>E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>($B$11)*(IF(B13&lt;=0,0,IF(B13&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))+(B13-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B13,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IF(C13&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D13*IF(($B$5+2*C13*SQRT(1+$B$7^2))&lt;=0,0,((D13/($B$5+2*C13*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>H13+I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="B14" s="19">
-        <f>A14-$B$10</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>MAX(0,A14-$B$4)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>IF(C14&lt;=0,0,($B$5+$B$7*C14)*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14*$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF(A14&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A14&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1))+(A14-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A14,Stage_Storage!$A$11:$A$18,1)))))</f>
-        <v/>
-      </c>
-      <c r="G14" s="13">
-        <f>E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>($B$11)*(IF(B14&lt;=0,0,IF(B14&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))+(B14-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B14,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF(C14&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D14*IF(($B$5+2*C14*SQRT(1+$B$7^2))&lt;=0,0,((D14/($B$5+2*C14*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>H14+I14</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>35.08</v>
+        <v>34.88</v>
       </c>
       <c r="B15" s="19">
         <f>A15-$B$10</f>
@@ -20454,7 +20444,7 @@
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B15&lt;=0,0,IF(B15&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1))+(B15-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B15,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I15" s="17">
@@ -20468,7 +20458,7 @@
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>35.18</v>
+        <v>34.98</v>
       </c>
       <c r="B16" s="19">
         <f>A16-$B$10</f>
@@ -20495,7 +20485,7 @@
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B16&lt;=0,0,IF(B16&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1))+(B16-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B16,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I16" s="17">
@@ -20509,7 +20499,7 @@
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>35.28</v>
+        <v>35.08</v>
       </c>
       <c r="B17" s="19">
         <f>A17-$B$10</f>
@@ -20536,7 +20526,7 @@
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B17&lt;=0,0,IF(B17&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1))+(B17-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B17,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I17" s="17">
@@ -20550,7 +20540,7 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>35.38</v>
+        <v>35.18</v>
       </c>
       <c r="B18" s="19">
         <f>A18-$B$10</f>
@@ -20577,7 +20567,7 @@
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B18&lt;=0,0,IF(B18&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1))+(B18-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B18,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I18" s="17">
@@ -20591,7 +20581,7 @@
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>35.48</v>
+        <v>35.28</v>
       </c>
       <c r="B19" s="19">
         <f>A19-$B$10</f>
@@ -20618,7 +20608,7 @@
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B19&lt;=0,0,IF(B19&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1))+(B19-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B19,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I19" s="17">
@@ -20632,7 +20622,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>35.58</v>
+        <v>35.38</v>
       </c>
       <c r="B20" s="19">
         <f>A20-$B$10</f>
@@ -20659,7 +20649,7 @@
         <v/>
       </c>
       <c r="H20" s="17">
-        <f>($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B20&lt;=0,0,IF(B20&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1))+(B20-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B20,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I20" s="17">
@@ -20673,7 +20663,7 @@
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>35.68</v>
+        <v>35.48</v>
       </c>
       <c r="B21" s="19">
         <f>A21-$B$10</f>
@@ -20700,7 +20690,7 @@
         <v/>
       </c>
       <c r="H21" s="17">
-        <f>($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B21&lt;=0,0,IF(B21&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1))+(B21-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B21,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I21" s="17">
@@ -20714,7 +20704,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>35.78</v>
+        <v>35.58</v>
       </c>
       <c r="B22" s="19">
         <f>A22-$B$10</f>
@@ -20741,7 +20731,7 @@
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B22&lt;=0,0,IF(B22&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1))+(B22-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B22,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I22" s="17">
@@ -20755,7 +20745,7 @@
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>35.88</v>
+        <v>35.68</v>
       </c>
       <c r="B23" s="19">
         <f>A23-$B$10</f>
@@ -20782,7 +20772,7 @@
         <v/>
       </c>
       <c r="H23" s="17">
-        <f>($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B23&lt;=0,0,IF(B23&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1))+(B23-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B23,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I23" s="17">
@@ -20796,7 +20786,7 @@
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>35.98</v>
+        <v>35.78</v>
       </c>
       <c r="B24" s="19">
         <f>A24-$B$10</f>
@@ -20823,7 +20813,7 @@
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B24&lt;=0,0,IF(B24&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1))+(B24-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B24,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -20837,7 +20827,7 @@
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>36.08</v>
+        <v>35.88</v>
       </c>
       <c r="B25" s="19">
         <f>A25-$B$10</f>
@@ -20864,7 +20854,7 @@
         <v/>
       </c>
       <c r="H25" s="17">
-        <f>($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B25&lt;=0,0,IF(B25&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1))+(B25-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B25,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -20878,7 +20868,7 @@
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
       <c r="B26" s="19">
         <f>A26-$B$10</f>
@@ -20905,7 +20895,7 @@
         <v/>
       </c>
       <c r="H26" s="17">
-        <f>($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B26&lt;=0,0,IF(B26&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1))+(B26-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B26,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -20919,7 +20909,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>36.28</v>
+        <v>36.08</v>
       </c>
       <c r="B27" s="19">
         <f>A27-$B$10</f>
@@ -20946,7 +20936,7 @@
         <v/>
       </c>
       <c r="H27" s="17">
-        <f>($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B27&lt;=0,0,IF(B27&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1))+(B27-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B27,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -20960,7 +20950,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>36.38</v>
+        <v>36.18</v>
       </c>
       <c r="B28" s="19">
         <f>A28-$B$10</f>
@@ -20987,7 +20977,7 @@
         <v/>
       </c>
       <c r="H28" s="17">
-        <f>($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B28&lt;=0,0,IF(B28&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1))+(B28-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B28,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I28" s="17">
@@ -21001,7 +20991,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>36.48</v>
+        <v>36.28</v>
       </c>
       <c r="B29" s="19">
         <f>A29-$B$10</f>
@@ -21028,7 +21018,7 @@
         <v/>
       </c>
       <c r="H29" s="17">
-        <f>($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B29&lt;=0,0,IF(B29&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1))+(B29-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B29,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I29" s="17">
@@ -21042,7 +21032,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>36.58</v>
+        <v>36.38</v>
       </c>
       <c r="B30" s="19">
         <f>A30-$B$10</f>
@@ -21069,7 +21059,7 @@
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B30&lt;=0,0,IF(B30&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1))+(B30-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B30,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I30" s="17">
@@ -21083,7 +21073,7 @@
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>36.68</v>
+        <v>36.48</v>
       </c>
       <c r="B31" s="19">
         <f>A31-$B$10</f>
@@ -21110,7 +21100,7 @@
         <v/>
       </c>
       <c r="H31" s="17">
-        <f>($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B31&lt;=0,0,IF(B31&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1))+(B31-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B31,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I31" s="17">
@@ -21124,7 +21114,7 @@
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>36.78</v>
+        <v>36.58</v>
       </c>
       <c r="B32" s="19">
         <f>A32-$B$10</f>
@@ -21151,7 +21141,7 @@
         <v/>
       </c>
       <c r="H32" s="17">
-        <f>($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B32&lt;=0,0,IF(B32&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1))+(B32-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B32,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I32" s="17">
@@ -21165,7 +21155,7 @@
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>36.88</v>
+        <v>36.68</v>
       </c>
       <c r="B33" s="19">
         <f>A33-$B$10</f>
@@ -21192,7 +21182,7 @@
         <v/>
       </c>
       <c r="H33" s="17">
-        <f>($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B33&lt;=0,0,IF(B33&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1))+(B33-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B33,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -21206,7 +21196,7 @@
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>36.98</v>
+        <v>36.78</v>
       </c>
       <c r="B34" s="19">
         <f>A34-$B$10</f>
@@ -21233,7 +21223,7 @@
         <v/>
       </c>
       <c r="H34" s="17">
-        <f>($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B34&lt;=0,0,IF(B34&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1))+(B34-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B34,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I34" s="17">
@@ -21247,7 +21237,7 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>37.08</v>
+        <v>36.88</v>
       </c>
       <c r="B35" s="19">
         <f>A35-$B$10</f>
@@ -21274,7 +21264,7 @@
         <v/>
       </c>
       <c r="H35" s="17">
-        <f>($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B35&lt;=0,0,IF(B35&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1))+(B35-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B35,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -21288,7 +21278,7 @@
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>37.18</v>
+        <v>36.98</v>
       </c>
       <c r="B36" s="19">
         <f>A36-$B$10</f>
@@ -21315,7 +21305,7 @@
         <v/>
       </c>
       <c r="H36" s="17">
-        <f>($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B36&lt;=0,0,IF(B36&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1))+(B36-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B36,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -21329,7 +21319,7 @@
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>37.28</v>
+        <v>37.08</v>
       </c>
       <c r="B37" s="19">
         <f>A37-$B$10</f>
@@ -21356,7 +21346,7 @@
         <v/>
       </c>
       <c r="H37" s="17">
-        <f>($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B37&lt;=0,0,IF(B37&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1))+(B37-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B37,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I37" s="17">
@@ -21370,7 +21360,7 @@
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>37.38</v>
+        <v>37.18</v>
       </c>
       <c r="B38" s="19">
         <f>A38-$B$10</f>
@@ -21397,7 +21387,7 @@
         <v/>
       </c>
       <c r="H38" s="17">
-        <f>($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B38&lt;=0,0,IF(B38&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1))+(B38-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B38,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -21411,7 +21401,7 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>37.48</v>
+        <v>37.28</v>
       </c>
       <c r="B39" s="19">
         <f>A39-$B$10</f>
@@ -21438,7 +21428,7 @@
         <v/>
       </c>
       <c r="H39" s="17">
-        <f>($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B39&lt;=0,0,IF(B39&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1))+(B39-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B39,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -21452,7 +21442,7 @@
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>37.58</v>
+        <v>37.38</v>
       </c>
       <c r="B40" s="19">
         <f>A40-$B$10</f>
@@ -21479,7 +21469,7 @@
         <v/>
       </c>
       <c r="H40" s="17">
-        <f>($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B40&lt;=0,0,IF(B40&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1))+(B40-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B40,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -21493,7 +21483,7 @@
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="B41" s="19">
         <f>A41-$B$10</f>
@@ -21520,7 +21510,7 @@
         <v/>
       </c>
       <c r="H41" s="17">
-        <f>($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B41&lt;=0,0,IF(B41&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1))+(B41-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B41,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -21534,7 +21524,7 @@
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>37.78</v>
+        <v>37.58</v>
       </c>
       <c r="B42" s="19">
         <f>A42-$B$10</f>
@@ -21561,7 +21551,7 @@
         <v/>
       </c>
       <c r="H42" s="17">
-        <f>($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B42&lt;=0,0,IF(B42&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1))+(B42-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B42,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I42" s="17">
@@ -21575,7 +21565,7 @@
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>37.88</v>
+        <v>37.68</v>
       </c>
       <c r="B43" s="19">
         <f>A43-$B$10</f>
@@ -21602,7 +21592,7 @@
         <v/>
       </c>
       <c r="H43" s="17">
-        <f>($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B43&lt;=0,0,IF(B43&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1))+(B43-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B43,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -21616,7 +21606,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>37.98</v>
+        <v>37.78</v>
       </c>
       <c r="B44" s="19">
         <f>A44-$B$10</f>
@@ -21643,7 +21633,7 @@
         <v/>
       </c>
       <c r="H44" s="17">
-        <f>($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B44&lt;=0,0,IF(B44&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1))+(B44-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B44,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -21657,7 +21647,7 @@
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>38.08</v>
+        <v>37.88</v>
       </c>
       <c r="B45" s="19">
         <f>A45-$B$10</f>
@@ -21684,7 +21674,7 @@
         <v/>
       </c>
       <c r="H45" s="17">
-        <f>($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B45&lt;=0,0,IF(B45&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1))+(B45-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B45,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -21698,7 +21688,7 @@
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>38.18</v>
+        <v>37.98</v>
       </c>
       <c r="B46" s="19">
         <f>A46-$B$10</f>
@@ -21725,7 +21715,7 @@
         <v/>
       </c>
       <c r="H46" s="17">
-        <f>($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B46&lt;=0,0,IF(B46&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1))+(B46-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B46,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -21739,7 +21729,7 @@
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>38.28</v>
+        <v>38.08</v>
       </c>
       <c r="B47" s="19">
         <f>A47-$B$10</f>
@@ -21766,7 +21756,7 @@
         <v/>
       </c>
       <c r="H47" s="17">
-        <f>($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B47&lt;=0,0,IF(B47&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1))+(B47-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B47,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I47" s="17">
@@ -21780,7 +21770,7 @@
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>38.38</v>
+        <v>38.18</v>
       </c>
       <c r="B48" s="19">
         <f>A48-$B$10</f>
@@ -21807,7 +21797,7 @@
         <v/>
       </c>
       <c r="H48" s="17">
-        <f>($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B48&lt;=0,0,IF(B48&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1))+(B48-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B48,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -21821,7 +21811,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>38.48</v>
+        <v>38.28</v>
       </c>
       <c r="B49" s="19">
         <f>A49-$B$10</f>
@@ -21848,7 +21838,7 @@
         <v/>
       </c>
       <c r="H49" s="17">
-        <f>($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B49&lt;=0,0,IF(B49&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1))+(B49-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B49,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -21862,7 +21852,7 @@
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>38.58</v>
+        <v>38.38</v>
       </c>
       <c r="B50" s="19">
         <f>A50-$B$10</f>
@@ -21889,7 +21879,7 @@
         <v/>
       </c>
       <c r="H50" s="17">
-        <f>($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B50&lt;=0,0,IF(B50&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1))+(B50-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B50,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -21903,7 +21893,7 @@
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>38.68</v>
+        <v>38.48</v>
       </c>
       <c r="B51" s="19">
         <f>A51-$B$10</f>
@@ -21930,7 +21920,7 @@
         <v/>
       </c>
       <c r="H51" s="17">
-        <f>($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B51&lt;=0,0,IF(B51&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1))+(B51-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B51,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -21944,7 +21934,7 @@
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="B52" s="19">
         <f>A52-$B$10</f>
@@ -21971,7 +21961,7 @@
         <v/>
       </c>
       <c r="H52" s="17">
-        <f>($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B52&lt;=0,0,IF(B52&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1))+(B52-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B52,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I52" s="17">
@@ -21985,7 +21975,7 @@
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="B53" s="19">
         <f>A53-$B$10</f>
@@ -22012,7 +22002,7 @@
         <v/>
       </c>
       <c r="H53" s="17">
-        <f>($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B53&lt;=0,0,IF(B53&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1))+(B53-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B53,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -22026,7 +22016,7 @@
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>38.98</v>
+        <v>38.78</v>
       </c>
       <c r="B54" s="19">
         <f>A54-$B$10</f>
@@ -22053,7 +22043,7 @@
         <v/>
       </c>
       <c r="H54" s="17">
-        <f>($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B54&lt;=0,0,IF(B54&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1))+(B54-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B54,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -22067,7 +22057,7 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>39.08</v>
+        <v>38.88</v>
       </c>
       <c r="B55" s="19">
         <f>A55-$B$10</f>
@@ -22094,7 +22084,7 @@
         <v/>
       </c>
       <c r="H55" s="17">
-        <f>($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B55&lt;=0,0,IF(B55&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1))+(B55-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B55,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -22108,7 +22098,7 @@
     </row>
     <row r="56">
       <c r="A56" s="19" t="n">
-        <v>39.18</v>
+        <v>38.98</v>
       </c>
       <c r="B56" s="19">
         <f>A56-$B$10</f>
@@ -22135,7 +22125,7 @@
         <v/>
       </c>
       <c r="H56" s="17">
-        <f>($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B56&lt;=0,0,IF(B56&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1))+(B56-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B56,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -22149,7 +22139,7 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="n">
-        <v>39.28</v>
+        <v>39.08</v>
       </c>
       <c r="B57" s="19">
         <f>A57-$B$10</f>
@@ -22176,7 +22166,7 @@
         <v/>
       </c>
       <c r="H57" s="17">
-        <f>($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B57&lt;=0,0,IF(B57&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1))+(B57-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B57,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -22190,7 +22180,7 @@
     </row>
     <row r="58">
       <c r="A58" s="19" t="n">
-        <v>39.38</v>
+        <v>39.18</v>
       </c>
       <c r="B58" s="19">
         <f>A58-$B$10</f>
@@ -22217,7 +22207,7 @@
         <v/>
       </c>
       <c r="H58" s="17">
-        <f>($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B58&lt;=0,0,IF(B58&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1))+(B58-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B58,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -22231,7 +22221,7 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="n">
-        <v>39.48</v>
+        <v>39.28</v>
       </c>
       <c r="B59" s="19">
         <f>A59-$B$10</f>
@@ -22258,7 +22248,7 @@
         <v/>
       </c>
       <c r="H59" s="17">
-        <f>($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B59&lt;=0,0,IF(B59&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1))+(B59-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B59,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -22272,7 +22262,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="n">
-        <v>39.58</v>
+        <v>39.38</v>
       </c>
       <c r="B60" s="19">
         <f>A60-$B$10</f>
@@ -22299,7 +22289,7 @@
         <v/>
       </c>
       <c r="H60" s="17">
-        <f>($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B60&lt;=0,0,IF(B60&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1))+(B60-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B60,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -22313,7 +22303,7 @@
     </row>
     <row r="61">
       <c r="A61" s="19" t="n">
-        <v>39.68</v>
+        <v>39.48</v>
       </c>
       <c r="B61" s="19">
         <f>A61-$B$10</f>
@@ -22340,7 +22330,7 @@
         <v/>
       </c>
       <c r="H61" s="17">
-        <f>($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B61&lt;=0,0,IF(B61&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1))+(B61-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B61,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -22354,7 +22344,7 @@
     </row>
     <row r="62">
       <c r="A62" s="19" t="n">
-        <v>39.78</v>
+        <v>39.58</v>
       </c>
       <c r="B62" s="19">
         <f>A62-$B$10</f>
@@ -22381,7 +22371,7 @@
         <v/>
       </c>
       <c r="H62" s="17">
-        <f>($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B62&lt;=0,0,IF(B62&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1))+(B62-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B62,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I62" s="17">
@@ -22395,7 +22385,7 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="n">
-        <v>39.88</v>
+        <v>39.68</v>
       </c>
       <c r="B63" s="19">
         <f>A63-$B$10</f>
@@ -22422,7 +22412,7 @@
         <v/>
       </c>
       <c r="H63" s="17">
-        <f>($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B63&lt;=0,0,IF(B63&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1))+(B63-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B63,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -22436,7 +22426,7 @@
     </row>
     <row r="64">
       <c r="A64" s="19" t="n">
-        <v>39.98</v>
+        <v>39.78</v>
       </c>
       <c r="B64" s="19">
         <f>A64-$B$10</f>
@@ -22463,7 +22453,7 @@
         <v/>
       </c>
       <c r="H64" s="17">
-        <f>($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))))))</f>
+        <f>MIN($B$12,($B$11)*(IF(B64&lt;=0,0,IF(B64&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1))+(B64-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B64,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -22472,6 +22462,88 @@
       </c>
       <c r="J64" s="8">
         <f>H64+I64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="B65" s="19">
+        <f>A65-$B$10</f>
+        <v/>
+      </c>
+      <c r="C65" s="19">
+        <f>MAX(0,A65-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(C65&lt;=0,0,($B$5+$B$7*C65)*C65)</f>
+        <v/>
+      </c>
+      <c r="E65" s="16">
+        <f>D65*$B$9</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(A65&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A65&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1))+(A65-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A65,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G65" s="13">
+        <f>E65+F65</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B65&lt;=0,0,IF(B65&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1))+(B65-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B65,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>IF(C65&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D65*IF(($B$5+2*C65*SQRT(1+$B$7^2))&lt;=0,0,((D65/($B$5+2*C65*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>H65+I65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="B66" s="19">
+        <f>A66-$B$10</f>
+        <v/>
+      </c>
+      <c r="C66" s="19">
+        <f>MAX(0,A66-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(C66&lt;=0,0,($B$5+$B$7*C66)*C66)</f>
+        <v/>
+      </c>
+      <c r="E66" s="16">
+        <f>D66*$B$9</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(A66&lt;=INDEX(Stage_Storage!$A$11:$A$18,1),INDEX(Stage_Storage!$E$11:$E$18,1),IF(A66&gt;=INDEX(Stage_Storage!$A$11:$A$18,ROWS(Stage_Storage!$A$11:$A$18)),INDEX(Stage_Storage!$E$11:$E$18,ROWS(Stage_Storage!$E$11:$E$18)),INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1))+(A66-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))/(INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$A$11:$A$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))*(INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)+1)-INDEX(Stage_Storage!$E$11:$E$18,MATCH(A66,Stage_Storage!$A$11:$A$18,1)))))</f>
+        <v/>
+      </c>
+      <c r="G66" s="13">
+        <f>E66+F66</f>
+        <v/>
+      </c>
+      <c r="H66" s="17">
+        <f>MIN($B$12,($B$11)*(IF(B66&lt;=0,0,IF(B66&gt;=INDEX(Courbe_QH_1200!$A$20:$A$80,ROWS(Courbe_QH_1200!$A$20:$A$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,ROWS(Courbe_QH_1200!$E$20:$E$80)),INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1))+(B66-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))/(INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$A$20:$A$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))*(INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)+1)-INDEX(Courbe_QH_1200!$E$20:$E$80,MATCH(B66,Courbe_QH_1200!$A$20:$A$80,1)))))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="17">
+        <f>IF(C66&lt;=0,0,IF($B$6&lt;=0,0,(1/$B$6)*D66*IF(($B$5+2*C66*SQRT(1+$B$7^2))&lt;=0,0,((D66/($B$5+2*C66*SQRT(1+$B$7^2)))^(2/3)))*SQRT($B$8)))</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>H66+I66</f>
         <v/>
       </c>
     </row>
